--- a/output/pdf_financials_xlsx/QNC.xlsx
+++ b/output/pdf_financials_xlsx/QNC.xlsx
@@ -1233,28 +1233,28 @@
         </is>
       </c>
       <c r="F16" s="3" t="n">
-        <v>1.431441</v>
+        <v>-1.431441</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>0.916042</v>
+        <v>-0.916042</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>0.663318</v>
+        <v>-0.663318</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>0.799251</v>
+        <v>-0.799251</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>1.562648</v>
+        <v>-1.562648</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>2.80457</v>
+        <v>-2.80457</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>2.386775</v>
+        <v>-2.386775</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>2.968738</v>
+        <v>-2.968738</v>
       </c>
       <c r="N16" s="1" t="inlineStr">
         <is>
@@ -1489,28 +1489,28 @@
         </is>
       </c>
       <c r="F20" s="3" t="n">
-        <v>1.431441</v>
+        <v>-1.431441</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>0.916042</v>
+        <v>-0.916042</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>0.663318</v>
+        <v>-0.663318</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>0.799251</v>
+        <v>-0.799251</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>1.562648</v>
+        <v>-1.562648</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>2.80457</v>
+        <v>-2.80457</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>2.386775</v>
+        <v>-2.386775</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>2.968738</v>
+        <v>-2.968738</v>
       </c>
       <c r="N20" s="1" t="inlineStr">
         <is>
@@ -1657,28 +1657,28 @@
         </is>
       </c>
       <c r="F23" s="3" t="n">
-        <v>1.431441</v>
+        <v>-1.431441</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>0.916042</v>
+        <v>-0.916042</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>0.663318</v>
+        <v>-0.663318</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>0.799251</v>
+        <v>-0.799251</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>1.562648</v>
+        <v>-1.562648</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>2.80457</v>
+        <v>-2.80457</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>2.386775</v>
+        <v>-2.386775</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>2.968738</v>
+        <v>-2.968738</v>
       </c>
       <c r="N23" s="1" t="inlineStr">
         <is>
@@ -1825,10 +1825,10 @@
         </is>
       </c>
       <c r="F26" s="3" t="n">
-        <v>47.7147</v>
+        <v>-47.7147</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>45.8021</v>
+        <v>-45.8021</v>
       </c>
       <c r="H26" s="1" t="inlineStr">
         <is>
@@ -1836,19 +1836,19 @@
         </is>
       </c>
       <c r="I26" s="3" t="n">
-        <v>61.480846</v>
+        <v>-61.480846</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>104.176533</v>
+        <v>-104.176533</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>133.550952</v>
+        <v>-133.550952</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>132.598611</v>
+        <v>-132.598611</v>
       </c>
       <c r="M26" s="3" t="n">
-        <v>148.4369</v>
+        <v>-148.4369</v>
       </c>
       <c r="N26" s="1" t="inlineStr">
         <is>
@@ -1883,28 +1883,28 @@
         </is>
       </c>
       <c r="F27" s="3" t="n">
-        <v>1.431441</v>
+        <v>-1.431441</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>0.916042</v>
+        <v>-0.916042</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>0.663318</v>
+        <v>-0.663318</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>0.799251</v>
+        <v>-0.799251</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>1.562648</v>
+        <v>-1.562648</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>2.80457</v>
+        <v>-2.80457</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>2.386775</v>
+        <v>-2.386775</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>2.968738</v>
+        <v>-2.968738</v>
       </c>
       <c r="N27" s="1" t="inlineStr">
         <is>
@@ -1995,28 +1995,28 @@
         </is>
       </c>
       <c r="F29" s="3" t="n">
-        <v>1.431441</v>
+        <v>-1.431441</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>0.916042</v>
+        <v>-0.916042</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>0.663318</v>
+        <v>-0.663318</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>0.799251</v>
+        <v>-0.799251</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>1.562648</v>
+        <v>-1.562648</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>2.80457</v>
+        <v>-2.80457</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>2.386775</v>
+        <v>-2.386775</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>2.968738</v>
+        <v>-2.968738</v>
       </c>
       <c r="N29" s="1" t="inlineStr">
         <is>
@@ -2123,28 +2123,28 @@
         </is>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="N31" s="1" t="inlineStr">
         <is>
@@ -5390,7 +5390,7 @@
         <v>0</v>
       </c>
       <c r="N91" s="3" t="n">
-        <v>0</v>
+        <v>0.29524</v>
       </c>
     </row>
     <row r="92">
@@ -5420,13 +5420,13 @@
         </is>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.682769</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.80108</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>0.782829</v>
       </c>
       <c r="I92" s="3" t="n">
         <v>0.280404</v>
@@ -9717,7 +9717,11 @@
           <t>Fair value reserve 15</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E24" t="inlineStr">
         <is>
           <t>-</t>
@@ -12034,7 +12038,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr"/>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E53" t="inlineStr">
         <is>
           <t>-</t>
@@ -22569,13 +22577,13 @@
         </is>
       </c>
       <c r="N185" s="5" t="n">
-        <v>2.80457</v>
+        <v>-2.80457</v>
       </c>
       <c r="O185" s="5" t="n">
-        <v>2.386775</v>
+        <v>-2.386775</v>
       </c>
       <c r="P185" s="5" t="n">
-        <v>2.968738</v>
+        <v>-2.968738</v>
       </c>
       <c r="Q185" t="inlineStr">
         <is>
@@ -26056,10 +26064,10 @@
         </is>
       </c>
       <c r="M229" s="5" t="n">
-        <v>1.562648</v>
+        <v>-1.562648</v>
       </c>
       <c r="N229" s="5" t="n">
-        <v>2.80457</v>
+        <v>-2.80457</v>
       </c>
       <c r="O229" t="inlineStr">
         <is>
@@ -27738,10 +27746,10 @@
         </is>
       </c>
       <c r="L250" s="5" t="n">
-        <v>0.799251</v>
+        <v>-0.799251</v>
       </c>
       <c r="M250" s="5" t="n">
-        <v>1.562648</v>
+        <v>-1.562648</v>
       </c>
       <c r="N250" t="inlineStr">
         <is>
@@ -29909,10 +29917,10 @@
         </is>
       </c>
       <c r="J277" s="5" t="n">
-        <v>0.916042</v>
+        <v>-0.916042</v>
       </c>
       <c r="K277" s="5" t="n">
-        <v>0.663318</v>
+        <v>-0.663318</v>
       </c>
       <c r="L277" t="inlineStr">
         <is>
@@ -31429,10 +31437,10 @@
         </is>
       </c>
       <c r="I296" s="5" t="n">
-        <v>1.431441</v>
+        <v>-1.431441</v>
       </c>
       <c r="J296" s="5" t="n">
-        <v>0.916042</v>
+        <v>-0.916042</v>
       </c>
       <c r="K296" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/QNC.xlsx
+++ b/output/pdf_financials_xlsx/QNC.xlsx
@@ -1009,13 +1009,13 @@
         </is>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.004272</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.008226000000000001</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.004433</v>
       </c>
       <c r="I12" s="3" t="n">
         <v>0</v>
@@ -1883,13 +1883,13 @@
         </is>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-1.431441</v>
+        <v>-1.435713</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-0.916042</v>
+        <v>-0.924268</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-0.663318</v>
+        <v>-0.667751</v>
       </c>
       <c r="I27" s="3" t="n">
         <v>-0.799251</v>
@@ -1995,13 +1995,13 @@
         </is>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-1.431441</v>
+        <v>-1.435713</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-0.916042</v>
+        <v>-0.924268</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-0.663318</v>
+        <v>-0.667751</v>
       </c>
       <c r="I29" s="3" t="n">
         <v>-0.799251</v>
@@ -2258,31 +2258,31 @@
         </is>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>1.189371</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.9095</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.287631</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.02009</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>1.021552</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>2.594051</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.315626</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>1.359406</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.246653</v>
       </c>
     </row>
     <row r="35">
@@ -2366,31 +2366,31 @@
         </is>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>1.189371</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.9095</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.287631</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.02009</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>1.021552</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>2.594051</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.315626</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>1.359406</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.246653</v>
       </c>
     </row>
     <row r="37">
@@ -3014,31 +3014,31 @@
         </is>
       </c>
       <c r="F48" s="3" t="n">
-        <v>1.208299</v>
+        <v>0.018928</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.977589</v>
+        <v>0.068089</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.297986</v>
+        <v>0.010355</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.033105</v>
+        <v>0.013015</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>2.143689</v>
+        <v>1.122137</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>3.663931</v>
+        <v>1.06988</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>1.240203</v>
+        <v>0.924577</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>1.52806</v>
+        <v>0.168654</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>37.736706</v>
+        <v>37.490053</v>
       </c>
     </row>
     <row r="49">
@@ -7183,7 +7183,7 @@
         <v>0</v>
       </c>
       <c r="N124" s="3" t="n">
-        <v>0</v>
+        <v>0.027622</v>
       </c>
     </row>
     <row r="125">
@@ -7239,7 +7239,7 @@
         <v>0</v>
       </c>
       <c r="N125" s="3" t="n">
-        <v>0</v>
+        <v>0.027622</v>
       </c>
     </row>
     <row r="126">
@@ -7955,7 +7955,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -11149,7 +11149,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -12362,7 +12362,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -14910,7 +14910,11 @@
           <t>Lease payments 8</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr"/>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E89" t="inlineStr">
         <is>
           <t>-</t>
@@ -29724,7 +29728,7 @@
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
@@ -31330,7 +31334,7 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">

--- a/output/pdf_financials_xlsx/QNC.xlsx
+++ b/output/pdf_financials_xlsx/QNC.xlsx
@@ -16148,7 +16148,11 @@
           <t>Additions to intangible assets 5</t>
         </is>
       </c>
-      <c r="D105" t="inlineStr"/>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E105" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/QNC.xlsx
+++ b/output/pdf_financials_xlsx/QNC.xlsx
@@ -5750,10 +5750,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F99" s="3" t="n">
+        <v>-1.431441</v>
       </c>
       <c r="G99" s="3" t="n">
         <v>-0.916042</v>
@@ -5808,10 +5806,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F100" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G100" s="3" t="n">
         <v>0</v>
@@ -5864,10 +5860,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F101" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G101" s="3" t="n">
         <v>0</v>
@@ -5920,10 +5914,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F102" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G102" s="3" t="n">
         <v>0</v>
@@ -5976,10 +5968,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F103" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G103" s="3" t="n">
         <v>0</v>
@@ -6032,10 +6022,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F104" s="3" t="n">
+        <v>0.051289</v>
       </c>
       <c r="G104" s="3" t="n">
         <v>-0.094737</v>
@@ -6088,10 +6076,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F105" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G105" s="3" t="n">
         <v>0</v>
@@ -6144,10 +6130,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F106" s="3" t="n">
+        <v>0.051289</v>
       </c>
       <c r="G106" s="3" t="n">
         <v>-0.094737</v>
@@ -6200,10 +6184,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F107" s="3" t="n">
+        <v>0.661385</v>
       </c>
       <c r="G107" s="3" t="n">
         <v>0.140016</v>
@@ -6256,10 +6238,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F108" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G108" s="3" t="n">
         <v>0</v>
@@ -6312,10 +6292,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F109" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G109" s="3" t="n">
         <v>0</v>
@@ -6368,10 +6346,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F110" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G110" s="3" t="n">
         <v>0</v>
@@ -6380,19 +6356,19 @@
         <v>0</v>
       </c>
       <c r="I110" s="3" t="n">
-        <v>0</v>
+        <v>0.00233</v>
       </c>
       <c r="J110" s="3" t="n">
-        <v>0</v>
+        <v>0.005529</v>
       </c>
       <c r="K110" s="3" t="n">
-        <v>0</v>
+        <v>0.006428</v>
       </c>
       <c r="L110" s="3" t="n">
         <v>0</v>
       </c>
       <c r="M110" s="3" t="n">
-        <v>0</v>
+        <v>0.006532</v>
       </c>
       <c r="N110" s="3" t="n">
         <v>0</v>
@@ -6424,10 +6400,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F111" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G111" s="3" t="n">
         <v>0</v>
@@ -6480,10 +6454,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F112" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G112" s="3" t="n">
         <v>0</v>
@@ -6536,10 +6508,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F113" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G113" s="3" t="n">
         <v>0</v>
@@ -6592,10 +6562,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F114" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G114" s="3" t="n">
         <v>0</v>
@@ -6607,13 +6575,13 @@
         <v>0</v>
       </c>
       <c r="J114" s="3" t="n">
-        <v>0</v>
+        <v>-1.464838</v>
       </c>
       <c r="K114" s="3" t="n">
-        <v>0</v>
+        <v>-1.170934</v>
       </c>
       <c r="L114" s="3" t="n">
-        <v>0</v>
+        <v>-0.336418</v>
       </c>
       <c r="M114" s="3" t="n">
         <v>1.245979</v>
@@ -6648,13 +6616,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F115" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G115" s="3" t="n">
-        <v>0</v>
+        <v>0.121845</v>
       </c>
       <c r="H115" s="3" t="n">
         <v>0</v>
@@ -6663,16 +6629,16 @@
         <v>0</v>
       </c>
       <c r="J115" s="3" t="n">
-        <v>0</v>
+        <v>0.464817</v>
       </c>
       <c r="K115" s="3" t="n">
-        <v>0</v>
+        <v>1.15763</v>
       </c>
       <c r="L115" s="3" t="n">
-        <v>0</v>
+        <v>0.489615</v>
       </c>
       <c r="M115" s="3" t="n">
-        <v>0</v>
+        <v>1.245979</v>
       </c>
       <c r="N115" s="3" t="n">
         <v>0</v>
@@ -6704,10 +6670,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F116" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G116" s="3" t="n">
         <v>0</v>
@@ -6760,10 +6724,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F117" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G117" s="3" t="n">
         <v>0</v>
@@ -6816,10 +6778,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F118" s="3" t="n">
+        <v>0.025</v>
       </c>
       <c r="G118" s="3" t="n">
         <v>0</v>
@@ -6932,10 +6892,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F120" s="3" t="n">
+        <v>0.02</v>
       </c>
       <c r="G120" s="3" t="n">
         <v>0</v>
@@ -6988,10 +6946,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F121" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G121" s="3" t="n">
         <v>0</v>
@@ -7044,10 +7000,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F122" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G122" s="3" t="n">
         <v>0</v>
@@ -7100,10 +7054,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F123" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G123" s="3" t="n">
         <v>0</v>
@@ -7156,10 +7108,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F124" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G124" s="3" t="n">
         <v>0</v>
@@ -7212,10 +7162,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F125" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G125" s="3" t="n">
         <v>0</v>
@@ -7268,10 +7216,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F126" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G126" s="3" t="n">
         <v>0</v>
@@ -7396,10 +7342,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F128" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G128" s="3" t="n">
         <v>0</v>
@@ -7514,10 +7458,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F130" s="3" t="n">
+        <v>0.987978</v>
       </c>
       <c r="G130" s="3" t="n">
         <v>1.189371</v>
@@ -7570,10 +7512,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F131" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G131" s="3" t="n">
         <v>0</v>
@@ -7626,10 +7566,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F132" s="3" t="n">
+        <v>0.201393</v>
       </c>
       <c r="G132" s="3" t="n">
         <v>-0.279871</v>
@@ -7682,10 +7620,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F133" s="3" t="n">
+        <v>1.189371</v>
       </c>
       <c r="G133" s="3" t="n">
         <v>0.9095</v>
@@ -7738,10 +7674,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F134" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G134" s="3" t="n">
         <v>0</v>
@@ -7841,7 +7775,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q305"/>
+  <dimension ref="A1:Q312"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -13573,7 +13507,11 @@
           <t>Accretion expense</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr"/>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E72" t="inlineStr">
         <is>
           <t>-</t>
@@ -13835,10 +13773,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I75" s="5" t="n">
+        <v>0.012203</v>
       </c>
       <c r="J75" s="5" t="n">
         <v>-0.037635</v>
@@ -13985,10 +13921,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I77" s="5" t="n">
+        <v>0.007607</v>
       </c>
       <c r="J77" s="5" t="n">
         <v>-0.012596</v>
@@ -14056,10 +13990,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I78" s="5" t="n">
+        <v>0.051289</v>
       </c>
       <c r="J78" s="5" t="n">
         <v>-0.094737</v>
@@ -15255,10 +15187,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I93" s="5" t="n">
+        <v>0.987978</v>
       </c>
       <c r="J93" s="5" t="n">
         <v>1.189371</v>
@@ -15326,10 +15256,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I94" s="5" t="n">
+        <v>1.189371</v>
       </c>
       <c r="J94" s="5" t="n">
         <v>0.9095</v>
@@ -15630,10 +15558,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I98" s="5" t="n">
+        <v>-1.431441</v>
       </c>
       <c r="J98" s="5" t="n">
         <v>-0.916042</v>
@@ -15832,7 +15758,11 @@
           <t>Accretion expense 7</t>
         </is>
       </c>
-      <c r="D101" t="inlineStr"/>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E101" t="inlineStr">
         <is>
           <t>-</t>
@@ -16229,7 +16159,11 @@
           <t>Acquisition of investments 4</t>
         </is>
       </c>
-      <c r="D106" t="inlineStr"/>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
       <c r="E106" t="inlineStr">
         <is>
           <t>-</t>
@@ -16304,7 +16238,11 @@
           <t>Proceeds from sale of investments 4</t>
         </is>
       </c>
-      <c r="D107" t="inlineStr"/>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E107" t="inlineStr">
         <is>
           <t>-</t>
@@ -17108,7 +17046,11 @@
           <t>Accretion expense</t>
         </is>
       </c>
-      <c r="D117" t="inlineStr"/>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E117" t="inlineStr">
         <is>
           <t>-</t>
@@ -18014,10 +17956,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I128" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I128" s="5" t="n">
+        <v>0.002007</v>
       </c>
       <c r="J128" s="5" t="n">
         <v>0.002007</v>
@@ -18330,10 +18270,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I132" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I132" s="5" t="n">
+        <v>-0.001353</v>
       </c>
       <c r="J132" s="5" t="n">
         <v>0.001353</v>
@@ -18897,10 +18835,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I139" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I139" s="5" t="n">
+        <v>-0.145</v>
       </c>
       <c r="J139" s="5" t="n">
         <v>0.048155</v>
@@ -19059,10 +18995,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I141" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I141" s="5" t="n">
+        <v>-0.868957</v>
       </c>
       <c r="J141" s="5" t="n">
         <v>-0.871769</v>
@@ -19196,7 +19130,11 @@
           <t>Proceeds from sale of investments</t>
         </is>
       </c>
-      <c r="D143" t="inlineStr"/>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E143" t="inlineStr">
         <is>
           <t>-</t>
@@ -19379,10 +19317,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I145" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I145" s="5" t="n">
+        <v>-0.1488</v>
       </c>
       <c r="J145" s="5" t="n">
         <v>0.095198</v>
@@ -19458,10 +19394,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I146" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I146" s="5" t="n">
+        <v>1.19915</v>
       </c>
       <c r="J146" s="5" t="n">
         <v>0.4967</v>
@@ -19539,10 +19473,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I147" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I147" s="5" t="n">
+        <v>1.21915</v>
       </c>
       <c r="J147" s="5" t="n">
         <v>0.4967</v>
@@ -19669,16 +19601,24 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr"/>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Adjustments to net loss for non-cash items</t>
+        </is>
+      </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Revenues 16</t>
-        </is>
-      </c>
-      <c r="D149" t="inlineStr"/>
+          <t>Share-based payments</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E149" t="inlineStr">
         <is>
           <t>-</t>
@@ -19699,15 +19639,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I149" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J149" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I149" s="5" t="n">
+        <v>0.661385</v>
+      </c>
+      <c r="J149" s="5" t="n">
+        <v>0.140016</v>
       </c>
       <c r="K149" t="inlineStr">
         <is>
@@ -19739,24 +19675,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Q149" s="5" t="n">
-        <v>0.011171</v>
+      <c r="Q149" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Adjustments to net loss for non-cash items</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Research and development 12</t>
+          <t>Gain on disposal of exploration and evaluation</t>
         </is>
       </c>
       <c r="D150" t="inlineStr"/>
@@ -19780,10 +19718,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I150" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I150" s="5" t="n">
+        <v>-0.025</v>
       </c>
       <c r="J150" t="inlineStr">
         <is>
@@ -19815,27 +19751,31 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P150" s="5" t="n">
-        <v>0.709379</v>
-      </c>
-      <c r="Q150" s="5" t="n">
-        <v>1.073747</v>
+      <c r="P150" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q150" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Investing Activities</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>General and administrative 12</t>
+          <t>Intellectual property acquisition</t>
         </is>
       </c>
       <c r="D151" t="inlineStr"/>
@@ -19859,15 +19799,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I151" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J151" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I151" s="5" t="n">
+        <v>-0.146377</v>
+      </c>
+      <c r="J151" s="5" t="n">
+        <v>-0.028</v>
       </c>
       <c r="K151" t="inlineStr">
         <is>
@@ -19894,27 +19830,31 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P151" s="5" t="n">
-        <v>1.644357</v>
-      </c>
-      <c r="Q151" s="5" t="n">
-        <v>2.239469</v>
+      <c r="P151" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q151" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Investing Activities</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Marketing 12</t>
+          <t>Advance to related party</t>
         </is>
       </c>
       <c r="D152" t="inlineStr"/>
@@ -19938,10 +19878,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I152" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I152" s="5" t="n">
+        <v>-0.00107</v>
       </c>
       <c r="J152" t="inlineStr">
         <is>
@@ -19973,30 +19911,38 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P152" s="5" t="n">
-        <v>0.183341</v>
-      </c>
-      <c r="Q152" s="5" t="n">
-        <v>0.836582</v>
+      <c r="P152" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q152" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Financing Activities</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Share-based payments 12,13</t>
-        </is>
-      </c>
-      <c r="D153" t="inlineStr"/>
+          <t>Proceeds from exercise of options</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>IssuanceOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E153" t="inlineStr">
         <is>
           <t>-</t>
@@ -20017,10 +19963,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I153" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I153" s="5" t="n">
+        <v>0.02</v>
       </c>
       <c r="J153" t="inlineStr">
         <is>
@@ -20052,30 +19996,38 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P153" s="5" t="n">
-        <v>0.399843</v>
-      </c>
-      <c r="Q153" s="5" t="n">
-        <v>6.833609</v>
+      <c r="P153" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q153" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Financing Activities</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Expenses total</t>
-        </is>
-      </c>
-      <c r="D154" t="inlineStr"/>
+          <t>Decrease/Increase in cash</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>ChangesInCash</t>
+        </is>
+      </c>
       <c r="E154" t="inlineStr">
         <is>
           <t>-</t>
@@ -20097,50 +20049,68 @@
         </is>
       </c>
       <c r="I154" s="5" t="n">
-        <v>1.608175</v>
+        <v>0.201393</v>
       </c>
       <c r="J154" s="5" t="n">
-        <v>0.871923</v>
-      </c>
-      <c r="K154" s="5" t="n">
-        <v>0.667752</v>
-      </c>
-      <c r="L154" s="5" t="n">
-        <v>0.809929</v>
-      </c>
-      <c r="M154" s="5" t="n">
-        <v>1.571811</v>
-      </c>
-      <c r="N154" s="5" t="n">
-        <v>2.738747</v>
-      </c>
-      <c r="O154" s="5" t="n">
-        <v>2.424206</v>
-      </c>
-      <c r="P154" s="5" t="n">
-        <v>2.93692</v>
-      </c>
-      <c r="Q154" s="5" t="n">
-        <v>10.983407</v>
+        <v>-0.279871</v>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L154" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M154" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N154" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O154" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P154" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q154" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Marketable securities received in consideration of the</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Amortization and depreciation 5,6</t>
-        </is>
-      </c>
-      <c r="D155" t="inlineStr"/>
+          <t>Marketable securities received in consideration of the disposal of exploration and evaluation assets</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E155" t="inlineStr">
         <is>
           <t>-</t>
@@ -20161,10 +20131,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I155" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I155" s="5" t="n">
+        <v>0.025</v>
       </c>
       <c r="J155" t="inlineStr">
         <is>
@@ -20196,11 +20164,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P155" s="5" t="n">
-        <v>0.022307</v>
-      </c>
-      <c r="Q155" s="5" t="n">
-        <v>0.049358</v>
+      <c r="P155" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q155" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="156">
@@ -20209,14 +20181,10 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>Other items</t>
-        </is>
-      </c>
+      <c r="B156" t="inlineStr"/>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Net financial (income) expense 14</t>
+          <t>Revenues 16</t>
         </is>
       </c>
       <c r="D156" t="inlineStr"/>
@@ -20275,11 +20243,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P156" s="5" t="n">
-        <v>0.009511</v>
+      <c r="P156" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="Q156" s="5" t="n">
-        <v>-0.473307</v>
+        <v>0.011171</v>
       </c>
     </row>
     <row r="157">
@@ -20290,12 +20260,12 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Other items total</t>
+          <t>Research and development 12</t>
         </is>
       </c>
       <c r="D157" t="inlineStr"/>
@@ -20339,20 +20309,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M157" s="5" t="n">
-        <v>-0.009162999999999999</v>
-      </c>
-      <c r="N157" s="5" t="n">
-        <v>0.06582300000000001</v>
-      </c>
-      <c r="O157" s="5" t="n">
-        <v>-0.037431</v>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N157" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O157" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="P157" s="5" t="n">
-        <v>0.031818</v>
+        <v>0.709379</v>
       </c>
       <c r="Q157" s="5" t="n">
-        <v>-0.423949</v>
+        <v>1.073747</v>
       </c>
     </row>
     <row r="158">
@@ -20363,12 +20339,12 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Net loss</t>
+          <t>General and administrative 12</t>
         </is>
       </c>
       <c r="D158" t="inlineStr"/>
@@ -20428,10 +20404,10 @@
         </is>
       </c>
       <c r="P158" s="5" t="n">
-        <v>2.968738</v>
+        <v>1.644357</v>
       </c>
       <c r="Q158" s="5" t="n">
-        <v>10.548287</v>
+        <v>2.239469</v>
       </c>
     </row>
     <row r="159">
@@ -20442,12 +20418,12 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Gain on equity instrument designated at fair</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Gain on equity instrument designated at fair value through other comprehensive income 4</t>
+          <t>Marketing 12</t>
         </is>
       </c>
       <c r="D159" t="inlineStr"/>
@@ -20506,13 +20482,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P159" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="P159" s="5" t="n">
+        <v>0.183341</v>
       </c>
       <c r="Q159" s="5" t="n">
-        <v>0.29524</v>
+        <v>0.836582</v>
       </c>
     </row>
     <row r="160">
@@ -20523,12 +20497,12 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Gain on equity instrument designated at fair</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Total comprehensive loss</t>
+          <t>Share-based payments 12,13</t>
         </is>
       </c>
       <c r="D160" t="inlineStr"/>
@@ -20588,10 +20562,10 @@
         </is>
       </c>
       <c r="P160" s="5" t="n">
-        <v>2.968738</v>
+        <v>0.399843</v>
       </c>
       <c r="Q160" s="5" t="n">
-        <v>10.253047</v>
+        <v>6.833609</v>
       </c>
     </row>
     <row r="161">
@@ -20602,12 +20576,12 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Gain on equity instrument designated at fair</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Basic and diluted loss per share</t>
+          <t>Expenses total</t>
         </is>
       </c>
       <c r="D161" t="inlineStr"/>
@@ -20631,46 +20605,32 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I161" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J161" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K161" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L161" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M161" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N161" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O161" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I161" s="5" t="n">
+        <v>1.608175</v>
+      </c>
+      <c r="J161" s="5" t="n">
+        <v>0.871923</v>
+      </c>
+      <c r="K161" s="5" t="n">
+        <v>0.667752</v>
+      </c>
+      <c r="L161" s="5" t="n">
+        <v>0.809929</v>
+      </c>
+      <c r="M161" s="5" t="n">
+        <v>1.571811</v>
+      </c>
+      <c r="N161" s="5" t="n">
+        <v>2.738747</v>
+      </c>
+      <c r="O161" s="5" t="n">
+        <v>2.424206</v>
       </c>
       <c r="P161" s="5" t="n">
-        <v>2e-08</v>
+        <v>2.93692</v>
       </c>
       <c r="Q161" s="5" t="n">
-        <v>5.5e-08</v>
+        <v>10.983407</v>
       </c>
     </row>
     <row r="162">
@@ -20681,12 +20641,12 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Gain on equity instrument designated at fair</t>
+          <t>Other items</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares</t>
+          <t>Amortization and depreciation 5,6</t>
         </is>
       </c>
       <c r="D162" t="inlineStr"/>
@@ -20746,10 +20706,10 @@
         </is>
       </c>
       <c r="P162" s="5" t="n">
-        <v>148.428317</v>
+        <v>0.022307</v>
       </c>
       <c r="Q162" s="5" t="n">
-        <v>186.699446</v>
+        <v>0.049358</v>
       </c>
     </row>
     <row r="163">
@@ -20760,12 +20720,12 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Balance as of</t>
+          <t>Other items</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>December 31, 2024 164,652,838 50,000 15,462,594 8,688 454,877 1,540,107 -</t>
+          <t>Net financial (income) expense 14</t>
         </is>
       </c>
       <c r="D163" t="inlineStr"/>
@@ -20825,10 +20785,10 @@
         </is>
       </c>
       <c r="P163" s="5" t="n">
-        <v>1.337843</v>
+        <v>0.009511</v>
       </c>
       <c r="Q163" s="5" t="n">
-        <v>-16.128423</v>
+        <v>-0.473307</v>
       </c>
     </row>
     <row r="164">
@@ -20839,12 +20799,12 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Balance as of</t>
+          <t>Other items</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Units issuance 12 21,333,333 (50,000) 11,755,676 (8,688) 10,253,012 - -</t>
+          <t>Other items total</t>
         </is>
       </c>
       <c r="D164" t="inlineStr"/>
@@ -20888,28 +20848,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M164" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N164" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O164" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M164" s="5" t="n">
+        <v>-0.009162999999999999</v>
+      </c>
+      <c r="N164" s="5" t="n">
+        <v>0.06582300000000001</v>
+      </c>
+      <c r="O164" s="5" t="n">
+        <v>-0.037431</v>
       </c>
       <c r="P164" s="5" t="n">
-        <v>22</v>
-      </c>
-      <c r="Q164" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.031818</v>
+      </c>
+      <c r="Q164" s="5" t="n">
+        <v>-0.423949</v>
       </c>
     </row>
     <row r="165">
@@ -20920,12 +20872,12 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Balance as of</t>
+          <t>Other items</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>- - Units issuance costs 12 (1,668,201) - - - -</t>
+          <t>Net loss</t>
         </is>
       </c>
       <c r="D165" t="inlineStr"/>
@@ -20985,12 +20937,10 @@
         </is>
       </c>
       <c r="P165" s="5" t="n">
-        <v>-1.668201</v>
-      </c>
-      <c r="Q165" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>2.968738</v>
+      </c>
+      <c r="Q165" s="5" t="n">
+        <v>10.548287</v>
       </c>
     </row>
     <row r="166">
@@ -21001,12 +20951,12 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Balance as of</t>
+          <t>Gain on equity instrument designated at fair</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Share-based payments 12 - - - - - 6,833,614 -</t>
+          <t>Gain on equity instrument designated at fair value through other comprehensive income 4</t>
         </is>
       </c>
       <c r="D166" t="inlineStr"/>
@@ -21065,13 +21015,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P166" s="5" t="n">
-        <v>6.833614</v>
-      </c>
-      <c r="Q166" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="P166" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q166" s="5" t="n">
+        <v>0.29524</v>
       </c>
     </row>
     <row r="167">
@@ -21082,12 +21032,12 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Balance as of</t>
+          <t>Gain on equity instrument designated at fair</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>- Exercise of options 12 2,212,500 999,078 - - (441,328) -</t>
+          <t>Total comprehensive loss</t>
         </is>
       </c>
       <c r="D167" t="inlineStr"/>
@@ -21147,12 +21097,10 @@
         </is>
       </c>
       <c r="P167" s="5" t="n">
-        <v>0.55775</v>
-      </c>
-      <c r="Q167" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>2.968738</v>
+      </c>
+      <c r="Q167" s="5" t="n">
+        <v>10.253047</v>
       </c>
     </row>
     <row r="168">
@@ -21163,12 +21111,12 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Balance as of</t>
+          <t>Gain on equity instrument designated at fair</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Exercise of warrants 12 30,389,999 - 31,561,309 - (8,130,276) - -</t>
+          <t>Basic and diluted loss per share</t>
         </is>
       </c>
       <c r="D168" t="inlineStr"/>
@@ -21228,12 +21176,10 @@
         </is>
       </c>
       <c r="P168" s="5" t="n">
-        <v>23.431033</v>
-      </c>
-      <c r="Q168" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>2e-08</v>
+      </c>
+      <c r="Q168" s="5" t="n">
+        <v>5.5e-08</v>
       </c>
     </row>
     <row r="169">
@@ -21244,12 +21190,12 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Balance as of</t>
+          <t>Gain on equity instrument designated at fair</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Total comprehensive loss - - - - - - 295,240</t>
+          <t>Weighted average number of common shares</t>
         </is>
       </c>
       <c r="D169" t="inlineStr"/>
@@ -21309,10 +21255,10 @@
         </is>
       </c>
       <c r="P169" s="5" t="n">
-        <v>-10.253047</v>
+        <v>148.428317</v>
       </c>
       <c r="Q169" s="5" t="n">
-        <v>-10.548287</v>
+        <v>186.699446</v>
       </c>
     </row>
     <row r="170">
@@ -21328,7 +21274,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>December 31, 2025 218,588,670 - 58,110,456 - 2,577,613 7,932,393 295,240</t>
+          <t>December 31, 2024 164,652,838 50,000 15,462,594 8,688 454,877 1,540,107 -</t>
         </is>
       </c>
       <c r="D170" t="inlineStr"/>
@@ -21388,10 +21334,10 @@
         </is>
       </c>
       <c r="P170" s="5" t="n">
-        <v>42.238991</v>
+        <v>1.337843</v>
       </c>
       <c r="Q170" s="5" t="n">
-        <v>-26.67671</v>
+        <v>-16.128423</v>
       </c>
     </row>
     <row r="171">
@@ -21407,7 +21353,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>December 31, 2023 135,502,838 - 13,413,478 - - 1,165,145 -</t>
+          <t>Units issuance 12 21,333,333 (50,000) 11,755,676 (8,688) 10,253,012 - -</t>
         </is>
       </c>
       <c r="D171" t="inlineStr"/>
@@ -21467,10 +21413,12 @@
         </is>
       </c>
       <c r="P171" s="5" t="n">
-        <v>1.418938</v>
-      </c>
-      <c r="Q171" s="5" t="n">
-        <v>-13.159685</v>
+        <v>22</v>
+      </c>
+      <c r="Q171" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="172">
@@ -21486,7 +21434,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Units issuance 12 22,500,000 - 891,893 - 608,107 - -</t>
+          <t>- - Units issuance costs 12 (1,668,201) - - - -</t>
         </is>
       </c>
       <c r="D172" t="inlineStr"/>
@@ -21546,7 +21494,7 @@
         </is>
       </c>
       <c r="P172" s="5" t="n">
-        <v>1.5</v>
+        <v>-1.668201</v>
       </c>
       <c r="Q172" t="inlineStr">
         <is>
@@ -21567,7 +21515,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Units issuance costs 12 - - (1,200) - - - -</t>
+          <t>Share-based payments 12 - - - - - 6,833,614 -</t>
         </is>
       </c>
       <c r="D173" t="inlineStr"/>
@@ -21627,7 +21575,7 @@
         </is>
       </c>
       <c r="P173" s="5" t="n">
-        <v>-0.0012</v>
+        <v>6.833614</v>
       </c>
       <c r="Q173" t="inlineStr">
         <is>
@@ -21648,7 +21596,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Share-based payments 12 - - - - - 399,843 -</t>
+          <t>- Exercise of options 12 2,212,500 999,078 - - (441,328) -</t>
         </is>
       </c>
       <c r="D174" t="inlineStr"/>
@@ -21708,7 +21656,7 @@
         </is>
       </c>
       <c r="P174" s="5" t="n">
-        <v>0.399843</v>
+        <v>0.55775</v>
       </c>
       <c r="Q174" t="inlineStr">
         <is>
@@ -21729,7 +21677,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Exercise of options 12 250,000 - 46,381 - - (24,881) -</t>
+          <t>Exercise of warrants 12 30,389,999 - 31,561,309 - (8,130,276) - -</t>
         </is>
       </c>
       <c r="D175" t="inlineStr"/>
@@ -21789,7 +21737,7 @@
         </is>
       </c>
       <c r="P175" s="5" t="n">
-        <v>0.0215</v>
+        <v>23.431033</v>
       </c>
       <c r="Q175" t="inlineStr">
         <is>
@@ -21810,7 +21758,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Exercise of warrants 12 6,400,000 50,000 1,112,042 8,688 (153,230) - -</t>
+          <t>Total comprehensive loss - - - - - - 295,240</t>
         </is>
       </c>
       <c r="D176" t="inlineStr"/>
@@ -21870,12 +21818,10 @@
         </is>
       </c>
       <c r="P176" s="5" t="n">
-        <v>0.9675</v>
-      </c>
-      <c r="Q176" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-10.253047</v>
+      </c>
+      <c r="Q176" s="5" t="n">
+        <v>-10.548287</v>
       </c>
     </row>
     <row r="177">
@@ -21891,7 +21837,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Total comprehensive loss - - - - - - -</t>
+          <t>December 31, 2025 218,588,670 - 58,110,456 - 2,577,613 7,932,393 295,240</t>
         </is>
       </c>
       <c r="D177" t="inlineStr"/>
@@ -21951,10 +21897,10 @@
         </is>
       </c>
       <c r="P177" s="5" t="n">
-        <v>-2.968738</v>
+        <v>42.238991</v>
       </c>
       <c r="Q177" s="5" t="n">
-        <v>-2.968738</v>
+        <v>-26.67671</v>
       </c>
     </row>
     <row r="178">
@@ -21965,19 +21911,15 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Balance as of</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Research and development 9</t>
-        </is>
-      </c>
-      <c r="D178" t="inlineStr">
-        <is>
-          <t>ResearchAndDevelopment</t>
-        </is>
-      </c>
+          <t>December 31, 2023 135,502,838 - 13,413,478 - - 1,165,145 -</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr"/>
       <c r="E178" t="inlineStr">
         <is>
           <t>-</t>
@@ -22023,19 +21965,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N178" s="5" t="n">
-        <v>0.271804</v>
-      </c>
-      <c r="O178" s="5" t="n">
-        <v>0.557108</v>
+      <c r="N178" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O178" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="P178" s="5" t="n">
-        <v>0.709379</v>
-      </c>
-      <c r="Q178" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1.418938</v>
+      </c>
+      <c r="Q178" s="5" t="n">
+        <v>-13.159685</v>
       </c>
     </row>
     <row r="179">
@@ -22046,19 +21990,15 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Balance as of</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>General and administrative 9</t>
-        </is>
-      </c>
-      <c r="D179" t="inlineStr">
-        <is>
-          <t>GeneralAndAdministrativeExpense</t>
-        </is>
-      </c>
+          <t>Units issuance 12 22,500,000 - 891,893 - 608,107 - -</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr"/>
       <c r="E179" t="inlineStr">
         <is>
           <t>-</t>
@@ -22104,14 +22044,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N179" s="5" t="n">
-        <v>1.210154</v>
-      </c>
-      <c r="O179" s="5" t="n">
-        <v>1.142557</v>
+      <c r="N179" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O179" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="P179" s="5" t="n">
-        <v>1.644357</v>
+        <v>1.5</v>
       </c>
       <c r="Q179" t="inlineStr">
         <is>
@@ -22127,19 +22071,15 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Balance as of</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Marketing</t>
-        </is>
-      </c>
-      <c r="D180" t="inlineStr">
-        <is>
-          <t>OtherOperatingExpenses</t>
-        </is>
-      </c>
+          <t>Units issuance costs 12 - - (1,200) - - - -</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr"/>
       <c r="E180" t="inlineStr">
         <is>
           <t>-</t>
@@ -22185,14 +22125,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N180" s="5" t="n">
-        <v>0.146218</v>
-      </c>
-      <c r="O180" s="5" t="n">
-        <v>0.229008</v>
+      <c r="N180" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O180" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="P180" s="5" t="n">
-        <v>0.183341</v>
+        <v>-0.0012</v>
       </c>
       <c r="Q180" t="inlineStr">
         <is>
@@ -22208,12 +22152,12 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Balance as of</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Share-based payments 8,9</t>
+          <t>Share-based payments 12 - - - - - 399,843 -</t>
         </is>
       </c>
       <c r="D181" t="inlineStr"/>
@@ -22262,11 +22206,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N181" s="5" t="n">
-        <v>0.541991</v>
-      </c>
-      <c r="O181" s="5" t="n">
-        <v>0.145533</v>
+      <c r="N181" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O181" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="P181" s="5" t="n">
         <v>0.399843</v>
@@ -22285,12 +22233,12 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Balance as of</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Impairment of intangible assets 5</t>
+          <t>Exercise of options 12 250,000 - 46,381 - - (24,881) -</t>
         </is>
       </c>
       <c r="D182" t="inlineStr"/>
@@ -22344,13 +22292,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O182" s="5" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="P182" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O182" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P182" s="5" t="n">
+        <v>0.0215</v>
       </c>
       <c r="Q182" t="inlineStr">
         <is>
@@ -22366,19 +22314,15 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Balance as of</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Amortization 4</t>
-        </is>
-      </c>
-      <c r="D183" t="inlineStr">
-        <is>
-          <t>Amortization</t>
-        </is>
-      </c>
+          <t>Exercise of warrants 12 6,400,000 50,000 1,112,042 8,688 (153,230) - -</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr"/>
       <c r="E183" t="inlineStr">
         <is>
           <t>-</t>
@@ -22429,11 +22373,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O183" s="5" t="n">
-        <v>0.022307</v>
+      <c r="O183" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="P183" s="5" t="n">
-        <v>0.022307</v>
+        <v>0.9675</v>
       </c>
       <c r="Q183" t="inlineStr">
         <is>
@@ -22449,12 +22395,12 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Balance as of</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Net financial (income) expense 10</t>
+          <t>Total comprehensive loss - - - - - - -</t>
         </is>
       </c>
       <c r="D184" t="inlineStr"/>
@@ -22503,19 +22449,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N184" s="5" t="n">
-        <v>0.043518</v>
-      </c>
-      <c r="O184" s="5" t="n">
-        <v>-0.059738</v>
+      <c r="N184" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O184" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="P184" s="5" t="n">
-        <v>0.009511</v>
-      </c>
-      <c r="Q184" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-2.968738</v>
+      </c>
+      <c r="Q184" s="5" t="n">
+        <v>-2.968738</v>
       </c>
     </row>
     <row r="185">
@@ -22526,17 +22474,17 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss</t>
+          <t>Research and development 9</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>ResearchAndDevelopment</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
@@ -22585,13 +22533,13 @@
         </is>
       </c>
       <c r="N185" s="5" t="n">
-        <v>-2.80457</v>
+        <v>0.271804</v>
       </c>
       <c r="O185" s="5" t="n">
-        <v>-2.386775</v>
+        <v>0.557108</v>
       </c>
       <c r="P185" s="5" t="n">
-        <v>-2.968738</v>
+        <v>0.709379</v>
       </c>
       <c r="Q185" t="inlineStr">
         <is>
@@ -22607,17 +22555,17 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Basic and diluted loss per share</t>
+          <t>General and administrative 9</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>BasicEPS</t>
+          <t>GeneralAndAdministrativeExpense</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
@@ -22666,13 +22614,13 @@
         </is>
       </c>
       <c r="N186" s="5" t="n">
-        <v>2.1e-08</v>
+        <v>1.210154</v>
       </c>
       <c r="O186" s="5" t="n">
-        <v>1.8e-08</v>
+        <v>1.142557</v>
       </c>
       <c r="P186" s="5" t="n">
-        <v>2e-08</v>
+        <v>1.644357</v>
       </c>
       <c r="Q186" t="inlineStr">
         <is>
@@ -22688,17 +22636,17 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>SharesOutstanding</t>
+          <t>OtherOperatingExpenses</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
@@ -22721,29 +22669,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I187" s="5" t="n">
-        <v>51.542664</v>
-      </c>
-      <c r="J187" s="5" t="n">
-        <v>60.352715</v>
-      </c>
-      <c r="K187" s="5" t="n">
-        <v>60.527838</v>
-      </c>
-      <c r="L187" s="5" t="n">
-        <v>60.527838</v>
-      </c>
-      <c r="M187" s="5" t="n">
-        <v>103.961043</v>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J187" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L187" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M187" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N187" s="5" t="n">
-        <v>134.474811</v>
+        <v>0.146218</v>
       </c>
       <c r="O187" s="5" t="n">
-        <v>135.502838</v>
+        <v>0.229008</v>
       </c>
       <c r="P187" s="5" t="n">
-        <v>148.428317</v>
+        <v>0.183341</v>
       </c>
       <c r="Q187" t="inlineStr">
         <is>
@@ -22759,12 +22717,12 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Balance as of</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>December 31, 2023 135,502,838 - 13,413,478 - 1,165,145</t>
+          <t>Share-based payments 8,9</t>
         </is>
       </c>
       <c r="D188" t="inlineStr"/>
@@ -22813,16 +22771,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N188" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N188" s="5" t="n">
+        <v>0.541991</v>
       </c>
       <c r="O188" s="5" t="n">
-        <v>1.418938</v>
+        <v>0.145533</v>
       </c>
       <c r="P188" s="5" t="n">
-        <v>-13.159685</v>
+        <v>0.399843</v>
       </c>
       <c r="Q188" t="inlineStr">
         <is>
@@ -22838,12 +22794,12 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Balance as of</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Units issuance 8 22,500,000 - 891,893 - 608,107 -</t>
+          <t>Impairment of intangible assets 5</t>
         </is>
       </c>
       <c r="D189" t="inlineStr"/>
@@ -22898,7 +22854,7 @@
         </is>
       </c>
       <c r="O189" s="5" t="n">
-        <v>1.5</v>
+        <v>0.35</v>
       </c>
       <c r="P189" t="inlineStr">
         <is>
@@ -22919,15 +22875,19 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Balance as of</t>
+          <t>Other items</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Units issuance costs 8 - - (1,200) - - -</t>
-        </is>
-      </c>
-      <c r="D190" t="inlineStr"/>
+          <t>Amortization 4</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>Amortization</t>
+        </is>
+      </c>
       <c r="E190" t="inlineStr">
         <is>
           <t>-</t>
@@ -22979,12 +22939,10 @@
         </is>
       </c>
       <c r="O190" s="5" t="n">
-        <v>-0.0012</v>
-      </c>
-      <c r="P190" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.022307</v>
+      </c>
+      <c r="P190" s="5" t="n">
+        <v>0.022307</v>
       </c>
       <c r="Q190" t="inlineStr">
         <is>
@@ -23000,12 +22958,12 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Balance as of</t>
+          <t>Other items</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Share-based payments 8 - - - - - 399,843</t>
+          <t>Net financial (income) expense 10</t>
         </is>
       </c>
       <c r="D191" t="inlineStr"/>
@@ -23054,18 +23012,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N191" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N191" s="5" t="n">
+        <v>0.043518</v>
       </c>
       <c r="O191" s="5" t="n">
-        <v>0.399843</v>
-      </c>
-      <c r="P191" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.059738</v>
+      </c>
+      <c r="P191" s="5" t="n">
+        <v>0.009511</v>
       </c>
       <c r="Q191" t="inlineStr">
         <is>
@@ -23081,15 +23035,19 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Balance as of</t>
+          <t>Other items</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Exercise of options 8 250,000 - 46,381 - - (24,881)</t>
-        </is>
-      </c>
-      <c r="D192" t="inlineStr"/>
+          <t>Net loss and comprehensive loss</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E192" t="inlineStr">
         <is>
           <t>-</t>
@@ -23135,18 +23093,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N192" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N192" s="5" t="n">
+        <v>-2.80457</v>
       </c>
       <c r="O192" s="5" t="n">
-        <v>0.0215</v>
-      </c>
-      <c r="P192" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-2.386775</v>
+      </c>
+      <c r="P192" s="5" t="n">
+        <v>-2.968738</v>
       </c>
       <c r="Q192" t="inlineStr">
         <is>
@@ -23162,15 +23116,19 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Balance as of</t>
+          <t>Other items</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Exercise of warrants 8 6,400,000 50,000 1,112,042 8,688 (153,230) -</t>
-        </is>
-      </c>
-      <c r="D193" t="inlineStr"/>
+          <t>Basic and diluted loss per share</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E193" t="inlineStr">
         <is>
           <t>-</t>
@@ -23216,18 +23174,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N193" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N193" s="5" t="n">
+        <v>2.1e-08</v>
       </c>
       <c r="O193" s="5" t="n">
-        <v>0.9675</v>
-      </c>
-      <c r="P193" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1.8e-08</v>
+      </c>
+      <c r="P193" s="5" t="n">
+        <v>2e-08</v>
       </c>
       <c r="Q193" t="inlineStr">
         <is>
@@ -23243,17 +23197,17 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Balance as of</t>
+          <t>Weighted average number of common shares</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Net loss - - - - - -</t>
+          <t>Weighted average number of common shares outstanding</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>SharesOutstanding</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
@@ -23276,41 +23230,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I194" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J194" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K194" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L194" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M194" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N194" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I194" s="5" t="n">
+        <v>51.542664</v>
+      </c>
+      <c r="J194" s="5" t="n">
+        <v>60.352715</v>
+      </c>
+      <c r="K194" s="5" t="n">
+        <v>60.527838</v>
+      </c>
+      <c r="L194" s="5" t="n">
+        <v>60.527838</v>
+      </c>
+      <c r="M194" s="5" t="n">
+        <v>103.961043</v>
+      </c>
+      <c r="N194" s="5" t="n">
+        <v>134.474811</v>
       </c>
       <c r="O194" s="5" t="n">
-        <v>-2.968738</v>
+        <v>135.502838</v>
       </c>
       <c r="P194" s="5" t="n">
-        <v>-2.968738</v>
+        <v>148.428317</v>
       </c>
       <c r="Q194" t="inlineStr">
         <is>
@@ -23331,7 +23273,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>December 31, 2024 164,652,838 50,000 15,462,594 8,688 454,877 1,540,107</t>
+          <t>December 31, 2023 135,502,838 - 13,413,478 - 1,165,145</t>
         </is>
       </c>
       <c r="D195" t="inlineStr"/>
@@ -23386,10 +23328,10 @@
         </is>
       </c>
       <c r="O195" s="5" t="n">
-        <v>1.337843</v>
+        <v>1.418938</v>
       </c>
       <c r="P195" s="5" t="n">
-        <v>-16.128423</v>
+        <v>-13.159685</v>
       </c>
       <c r="Q195" t="inlineStr">
         <is>
@@ -23410,7 +23352,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>December 31, 2022 135,502,838 - 13,413,478 - - 1,019,612</t>
+          <t>Units issuance 8 22,500,000 - 891,893 - 608,107 -</t>
         </is>
       </c>
       <c r="D196" t="inlineStr"/>
@@ -23465,10 +23407,12 @@
         </is>
       </c>
       <c r="O196" s="5" t="n">
-        <v>3.66018</v>
-      </c>
-      <c r="P196" s="5" t="n">
-        <v>-10.77291</v>
+        <v>1.5</v>
+      </c>
+      <c r="P196" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="Q196" t="inlineStr">
         <is>
@@ -23489,7 +23433,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Share-based payments 8 - - - - - 145,533</t>
+          <t>Units issuance costs 8 - - (1,200) - - -</t>
         </is>
       </c>
       <c r="D197" t="inlineStr"/>
@@ -23544,7 +23488,7 @@
         </is>
       </c>
       <c r="O197" s="5" t="n">
-        <v>0.145533</v>
+        <v>-0.0012</v>
       </c>
       <c r="P197" t="inlineStr">
         <is>
@@ -23570,7 +23514,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>December 31, 2023 135,502,838 - 13,413,478 - - 1,165,145</t>
+          <t>Share-based payments 8 - - - - - 399,843</t>
         </is>
       </c>
       <c r="D198" t="inlineStr"/>
@@ -23625,10 +23569,12 @@
         </is>
       </c>
       <c r="O198" s="5" t="n">
-        <v>1.418938</v>
-      </c>
-      <c r="P198" s="5" t="n">
-        <v>-13.159685</v>
+        <v>0.399843</v>
+      </c>
+      <c r="P198" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="Q198" t="inlineStr">
         <is>
@@ -23644,12 +23590,12 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Balance as of</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Loss on derecognition of intangible assets 5</t>
+          <t>Exercise of options 8 250,000 - 46,381 - - (24,881)</t>
         </is>
       </c>
       <c r="D199" t="inlineStr"/>
@@ -23698,13 +23644,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N199" s="5" t="n">
-        <v>0.56858</v>
-      </c>
-      <c r="O199" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N199" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O199" s="5" t="n">
+        <v>0.0215</v>
       </c>
       <c r="P199" t="inlineStr">
         <is>
@@ -23725,19 +23671,15 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Balance as of</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Amortization 5</t>
-        </is>
-      </c>
-      <c r="D200" t="inlineStr">
-        <is>
-          <t>Amortization</t>
-        </is>
-      </c>
+          <t>Exercise of warrants 8 6,400,000 50,000 1,112,042 8,688 (153,230) -</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr"/>
       <c r="E200" t="inlineStr">
         <is>
           <t>-</t>
@@ -23783,11 +23725,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N200" s="5" t="n">
-        <v>0.022305</v>
+      <c r="N200" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O200" s="5" t="n">
-        <v>0.022307</v>
+        <v>0.9675</v>
       </c>
       <c r="P200" t="inlineStr">
         <is>
@@ -23808,15 +23752,19 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Notes            shares                           surplus           Deficit          equity</t>
+          <t>Balance as of</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Balance as of December 31, 2022 135,502,838 13,413,478 1,019,612</t>
-        </is>
-      </c>
-      <c r="D201" t="inlineStr"/>
+          <t>Net loss - - - - - -</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E201" t="inlineStr">
         <is>
           <t>-</t>
@@ -23862,16 +23810,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N201" s="5" t="n">
-        <v>3.66018</v>
+      <c r="N201" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O201" s="5" t="n">
-        <v>-10.77291</v>
-      </c>
-      <c r="P201" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-2.968738</v>
+      </c>
+      <c r="P201" s="5" t="n">
+        <v>-2.968738</v>
       </c>
       <c r="Q201" t="inlineStr">
         <is>
@@ -23887,12 +23835,12 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Notes            shares                           surplus           Deficit          equity</t>
+          <t>Balance as of</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Share-based payments 8 - - 145,533</t>
+          <t>December 31, 2024 164,652,838 50,000 15,462,594 8,688 454,877 1,540,107</t>
         </is>
       </c>
       <c r="D202" t="inlineStr"/>
@@ -23941,18 +23889,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N202" s="5" t="n">
-        <v>0.145533</v>
-      </c>
-      <c r="O202" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P202" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N202" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O202" s="5" t="n">
+        <v>1.337843</v>
+      </c>
+      <c r="P202" s="5" t="n">
+        <v>-16.128423</v>
       </c>
       <c r="Q202" t="inlineStr">
         <is>
@@ -23968,19 +23914,15 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Notes            shares                           surplus           Deficit          equity</t>
+          <t>Balance as of</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Net loss - - -</t>
-        </is>
-      </c>
-      <c r="D203" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>December 31, 2022 135,502,838 - 13,413,478 - - 1,019,612</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr"/>
       <c r="E203" t="inlineStr">
         <is>
           <t>-</t>
@@ -24026,16 +23968,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N203" s="5" t="n">
-        <v>-2.386775</v>
+      <c r="N203" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O203" s="5" t="n">
-        <v>-2.386775</v>
-      </c>
-      <c r="P203" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>3.66018</v>
+      </c>
+      <c r="P203" s="5" t="n">
+        <v>-10.77291</v>
       </c>
       <c r="Q203" t="inlineStr">
         <is>
@@ -24051,12 +23993,12 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Notes            shares                           surplus           Deficit          equity</t>
+          <t>Balance as of</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Balance as of December 31, 2023 135,502,838 13,413,478 1,165,145</t>
+          <t>Share-based payments 8 - - - - - 145,533</t>
         </is>
       </c>
       <c r="D204" t="inlineStr"/>
@@ -24105,11 +24047,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N204" s="5" t="n">
-        <v>1.418938</v>
+      <c r="N204" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O204" s="5" t="n">
-        <v>-13.159685</v>
+        <v>0.145533</v>
       </c>
       <c r="P204" t="inlineStr">
         <is>
@@ -24130,12 +24074,12 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Notes            shares                           surplus           Deficit          equity</t>
+          <t>Balance as of</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Balance as of December 31, 2021 114,012,838 10,173,156 506,603</t>
+          <t>December 31, 2023 135,502,838 - 13,413,478 - - 1,165,145</t>
         </is>
       </c>
       <c r="D205" t="inlineStr"/>
@@ -24184,16 +24128,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N205" s="5" t="n">
-        <v>2.711419</v>
+      <c r="N205" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O205" s="5" t="n">
-        <v>-7.96834</v>
-      </c>
-      <c r="P205" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1.418938</v>
+      </c>
+      <c r="P205" s="5" t="n">
+        <v>-13.159685</v>
       </c>
       <c r="Q205" t="inlineStr">
         <is>
@@ -24209,12 +24153,12 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Notes            shares                           surplus           Deficit          equity</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Share-based payments 8 - - 541,991</t>
+          <t>Loss on derecognition of intangible assets 5</t>
         </is>
       </c>
       <c r="D206" t="inlineStr"/>
@@ -24264,7 +24208,7 @@
         </is>
       </c>
       <c r="N206" s="5" t="n">
-        <v>0.541991</v>
+        <v>0.56858</v>
       </c>
       <c r="O206" t="inlineStr">
         <is>
@@ -24290,15 +24234,19 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Notes            shares                           surplus           Deficit          equity</t>
+          <t>Other items</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Share issue costs - 340 -</t>
-        </is>
-      </c>
-      <c r="D207" t="inlineStr"/>
+          <t>Amortization 5</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>Amortization</t>
+        </is>
+      </c>
       <c r="E207" t="inlineStr">
         <is>
           <t>-</t>
@@ -24345,12 +24293,10 @@
         </is>
       </c>
       <c r="N207" s="5" t="n">
-        <v>0.00034</v>
-      </c>
-      <c r="O207" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.022305</v>
+      </c>
+      <c r="O207" s="5" t="n">
+        <v>0.022307</v>
       </c>
       <c r="P207" t="inlineStr">
         <is>
@@ -24376,7 +24322,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Exercise of options 8 250,000 53,982 (28,982)</t>
+          <t>Balance as of December 31, 2022 135,502,838 13,413,478 1,019,612</t>
         </is>
       </c>
       <c r="D208" t="inlineStr"/>
@@ -24426,12 +24372,10 @@
         </is>
       </c>
       <c r="N208" s="5" t="n">
-        <v>0.025</v>
-      </c>
-      <c r="O208" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>3.66018</v>
+      </c>
+      <c r="O208" s="5" t="n">
+        <v>-10.77291</v>
       </c>
       <c r="P208" t="inlineStr">
         <is>
@@ -24457,7 +24401,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Exercise of warrants 8 21,240,000 3,186,000 -</t>
+          <t>Share-based payments 8 - - 145,533</t>
         </is>
       </c>
       <c r="D209" t="inlineStr"/>
@@ -24507,7 +24451,7 @@
         </is>
       </c>
       <c r="N209" s="5" t="n">
-        <v>3.186</v>
+        <v>0.145533</v>
       </c>
       <c r="O209" t="inlineStr">
         <is>
@@ -24533,17 +24477,17 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Notes            shares                           surplus           Deficit          equity</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Management fees 9 $</t>
+          <t>Net loss - - -</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>NetIncome</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
@@ -24581,19 +24525,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L210" s="5" t="n">
-        <v>0.0306</v>
-      </c>
-      <c r="M210" s="5" t="n">
-        <v>0.3226</v>
+      <c r="L210" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M210" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N210" s="5" t="n">
-        <v>0.634746</v>
-      </c>
-      <c r="O210" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-2.386775</v>
+      </c>
+      <c r="O210" s="5" t="n">
+        <v>-2.386775</v>
       </c>
       <c r="P210" t="inlineStr">
         <is>
@@ -24614,12 +24560,12 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Notes            shares                           surplus           Deficit          equity</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Share-based payments 8, 9</t>
+          <t>Balance as of December 31, 2023 135,502,838 13,413,478 1,165,145</t>
         </is>
       </c>
       <c r="D211" t="inlineStr"/>
@@ -24658,19 +24604,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L211" s="5" t="n">
-        <v>0.1155</v>
-      </c>
-      <c r="M211" s="5" t="n">
-        <v>0.263745</v>
+      <c r="L211" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M211" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N211" s="5" t="n">
-        <v>0.541991</v>
-      </c>
-      <c r="O211" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1.418938</v>
+      </c>
+      <c r="O211" s="5" t="n">
+        <v>-13.159685</v>
       </c>
       <c r="P211" t="inlineStr">
         <is>
@@ -24691,19 +24639,15 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Notes            shares                           surplus           Deficit          equity</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Research and development</t>
-        </is>
-      </c>
-      <c r="D212" t="inlineStr">
-        <is>
-          <t>ResearchAndDevelopment</t>
-        </is>
-      </c>
+          <t>Balance as of December 31, 2021 114,012,838 10,173,156 506,603</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr"/>
       <c r="E212" t="inlineStr">
         <is>
           <t>-</t>
@@ -24744,16 +24688,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M212" s="5" t="n">
-        <v>0.117155</v>
+      <c r="M212" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N212" s="5" t="n">
-        <v>0.271804</v>
-      </c>
-      <c r="O212" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>2.711419</v>
+      </c>
+      <c r="O212" s="5" t="n">
+        <v>-7.96834</v>
       </c>
       <c r="P212" t="inlineStr">
         <is>
@@ -24774,19 +24718,15 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Notes            shares                           surplus           Deficit          equity</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Professional fees</t>
-        </is>
-      </c>
-      <c r="D213" t="inlineStr">
-        <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
-        </is>
-      </c>
+          <t>Share-based payments 8 - - 541,991</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr"/>
       <c r="E213" t="inlineStr">
         <is>
           <t>-</t>
@@ -24807,23 +24747,33 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I213" s="5" t="n">
-        <v>0.033437</v>
-      </c>
-      <c r="J213" s="5" t="n">
-        <v>0.031978</v>
-      </c>
-      <c r="K213" s="5" t="n">
-        <v>0.028537</v>
-      </c>
-      <c r="L213" s="5" t="n">
-        <v>0.19468</v>
-      </c>
-      <c r="M213" s="5" t="n">
-        <v>0.205187</v>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J213" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L213" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M213" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N213" s="5" t="n">
-        <v>0.242182</v>
+        <v>0.541991</v>
       </c>
       <c r="O213" t="inlineStr">
         <is>
@@ -24849,19 +24799,15 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Notes            shares                           surplus           Deficit          equity</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Office</t>
-        </is>
-      </c>
-      <c r="D214" t="inlineStr">
-        <is>
-          <t>OtherOperatingExpenses</t>
-        </is>
-      </c>
+          <t>Share issue costs - 340 -</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr"/>
       <c r="E214" t="inlineStr">
         <is>
           <t>-</t>
@@ -24882,23 +24828,33 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I214" s="5" t="n">
-        <v>0.029408</v>
-      </c>
-      <c r="J214" s="5" t="n">
-        <v>0.025132</v>
-      </c>
-      <c r="K214" s="5" t="n">
-        <v>0.023716</v>
-      </c>
-      <c r="L214" s="5" t="n">
-        <v>0.010767</v>
-      </c>
-      <c r="M214" s="5" t="n">
-        <v>0.06252199999999999</v>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J214" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L214" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M214" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N214" s="5" t="n">
-        <v>0.09624199999999999</v>
+        <v>0.00034</v>
       </c>
       <c r="O214" t="inlineStr">
         <is>
@@ -24924,12 +24880,12 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Notes            shares                           surplus           Deficit          equity</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Salaries</t>
+          <t>Exercise of options 8 250,000 53,982 (28,982)</t>
         </is>
       </c>
       <c r="D215" t="inlineStr"/>
@@ -24968,14 +24924,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L215" s="5" t="n">
-        <v>0.197363</v>
-      </c>
-      <c r="M215" s="5" t="n">
-        <v>0.027809</v>
+      <c r="L215" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M215" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N215" s="5" t="n">
-        <v>0.095955</v>
+        <v>0.025</v>
       </c>
       <c r="O215" t="inlineStr">
         <is>
@@ -25001,19 +24961,15 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Notes            shares                           surplus           Deficit          equity</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Investor relations</t>
-        </is>
-      </c>
-      <c r="D216" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Exercise of warrants 8 21,240,000 3,186,000 -</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr"/>
       <c r="E216" t="inlineStr">
         <is>
           <t>-</t>
@@ -25054,11 +25010,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M216" s="5" t="n">
-        <v>0.124873</v>
+      <c r="M216" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N216" s="5" t="n">
-        <v>0.069858</v>
+        <v>3.186</v>
       </c>
       <c r="O216" t="inlineStr">
         <is>
@@ -25089,10 +25047,14 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Filing and listing fees</t>
-        </is>
-      </c>
-      <c r="D217" t="inlineStr"/>
+          <t>Management fees 9 $</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E217" t="inlineStr">
         <is>
           <t>-</t>
@@ -25113,23 +25075,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I217" s="5" t="n">
-        <v>0.032711</v>
-      </c>
-      <c r="J217" s="5" t="n">
-        <v>0.029311</v>
-      </c>
-      <c r="K217" s="5" t="n">
-        <v>0.018058</v>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J217" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L217" s="5" t="n">
-        <v>0.026187</v>
+        <v>0.0306</v>
       </c>
       <c r="M217" s="5" t="n">
-        <v>0.142405</v>
+        <v>0.3226</v>
       </c>
       <c r="N217" s="5" t="n">
-        <v>0.044855</v>
+        <v>0.634746</v>
       </c>
       <c r="O217" t="inlineStr">
         <is>
@@ -25160,14 +25128,10 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Consulting fees</t>
-        </is>
-      </c>
-      <c r="D218" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Share-based payments 8, 9</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr"/>
       <c r="E218" t="inlineStr">
         <is>
           <t>-</t>
@@ -25204,13 +25168,13 @@
         </is>
       </c>
       <c r="L218" s="5" t="n">
-        <v>0.1864</v>
+        <v>0.1155</v>
       </c>
       <c r="M218" s="5" t="n">
-        <v>0.118909</v>
+        <v>0.263745</v>
       </c>
       <c r="N218" s="5" t="n">
-        <v>0.0444</v>
+        <v>0.541991</v>
       </c>
       <c r="O218" t="inlineStr">
         <is>
@@ -25241,12 +25205,12 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Travel</t>
+          <t>Research and development</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>ResearchAndDevelopment</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
@@ -25269,23 +25233,31 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I219" s="5" t="n">
-        <v>0.119836</v>
-      </c>
-      <c r="J219" s="5" t="n">
-        <v>0.092081</v>
-      </c>
-      <c r="K219" s="5" t="n">
-        <v>0.09388000000000001</v>
-      </c>
-      <c r="L219" s="5" t="n">
-        <v>0.008085</v>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J219" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L219" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M219" s="5" t="n">
-        <v>0.031962</v>
+        <v>0.117155</v>
       </c>
       <c r="N219" s="5" t="n">
-        <v>0.041514</v>
+        <v>0.271804</v>
       </c>
       <c r="O219" t="inlineStr">
         <is>
@@ -25316,10 +25288,14 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Promotion expenses</t>
-        </is>
-      </c>
-      <c r="D220" t="inlineStr"/>
+          <t>Professional fees</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
       <c r="E220" t="inlineStr">
         <is>
           <t>-</t>
@@ -25340,27 +25316,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I220" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I220" s="5" t="n">
+        <v>0.033437</v>
       </c>
       <c r="J220" s="5" t="n">
-        <v>0.011119</v>
+        <v>0.031978</v>
       </c>
       <c r="K220" s="5" t="n">
-        <v>0.006</v>
-      </c>
-      <c r="L220" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.028537</v>
+      </c>
+      <c r="L220" s="5" t="n">
+        <v>0.19468</v>
       </c>
       <c r="M220" s="5" t="n">
-        <v>0.047154</v>
+        <v>0.205187</v>
       </c>
       <c r="N220" s="5" t="n">
-        <v>0.034846</v>
+        <v>0.242182</v>
       </c>
       <c r="O220" t="inlineStr">
         <is>
@@ -25391,10 +25363,14 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Information technology</t>
-        </is>
-      </c>
-      <c r="D221" t="inlineStr"/>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E221" t="inlineStr">
         <is>
           <t>-</t>
@@ -25415,31 +25391,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I221" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J221" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K221" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L221" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I221" s="5" t="n">
+        <v>0.029408</v>
+      </c>
+      <c r="J221" s="5" t="n">
+        <v>0.025132</v>
+      </c>
+      <c r="K221" s="5" t="n">
+        <v>0.023716</v>
+      </c>
+      <c r="L221" s="5" t="n">
+        <v>0.010767</v>
       </c>
       <c r="M221" s="5" t="n">
-        <v>0.068786</v>
+        <v>0.06252199999999999</v>
       </c>
       <c r="N221" s="5" t="n">
-        <v>0.032091</v>
+        <v>0.09624199999999999</v>
       </c>
       <c r="O221" t="inlineStr">
         <is>
@@ -25470,14 +25438,10 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Amortization 5</t>
-        </is>
-      </c>
-      <c r="D222" t="inlineStr">
-        <is>
-          <t>Amortization</t>
-        </is>
-      </c>
+          <t>Salaries</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr"/>
       <c r="E222" t="inlineStr">
         <is>
           <t>-</t>
@@ -25514,13 +25478,13 @@
         </is>
       </c>
       <c r="L222" s="5" t="n">
-        <v>0.022305</v>
+        <v>0.197363</v>
       </c>
       <c r="M222" s="5" t="n">
-        <v>0.022305</v>
+        <v>0.027809</v>
       </c>
       <c r="N222" s="5" t="n">
-        <v>0.022305</v>
+        <v>0.095955</v>
       </c>
       <c r="O222" t="inlineStr">
         <is>
@@ -25551,7 +25515,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Investor relations</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -25579,23 +25543,31 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I223" s="5" t="n">
-        <v>0.010148</v>
-      </c>
-      <c r="J223" s="5" t="n">
-        <v>0.01377</v>
-      </c>
-      <c r="K223" s="5" t="n">
-        <v>0.01374</v>
-      </c>
-      <c r="L223" s="5" t="n">
-        <v>0.0145</v>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J223" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L223" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M223" s="5" t="n">
-        <v>0.016399</v>
+        <v>0.124873</v>
       </c>
       <c r="N223" s="5" t="n">
-        <v>0.019683</v>
+        <v>0.069858</v>
       </c>
       <c r="O223" t="inlineStr">
         <is>
@@ -25621,12 +25593,12 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Financial Income</t>
+          <t>Filing and listing fees</t>
         </is>
       </c>
       <c r="D224" t="inlineStr"/>
@@ -25650,31 +25622,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I224" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J224" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K224" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L224" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I224" s="5" t="n">
+        <v>0.032711</v>
+      </c>
+      <c r="J224" s="5" t="n">
+        <v>0.029311</v>
+      </c>
+      <c r="K224" s="5" t="n">
+        <v>0.018058</v>
+      </c>
+      <c r="L224" s="5" t="n">
+        <v>0.026187</v>
       </c>
       <c r="M224" s="5" t="n">
-        <v>0.001265</v>
+        <v>0.142405</v>
       </c>
       <c r="N224" s="5" t="n">
-        <v>0.07699499999999999</v>
+        <v>0.044855</v>
       </c>
       <c r="O224" t="inlineStr">
         <is>
@@ -25700,15 +25664,19 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Financial expenses</t>
-        </is>
-      </c>
-      <c r="D225" t="inlineStr"/>
+          <t>Consulting fees</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E225" t="inlineStr">
         <is>
           <t>-</t>
@@ -25744,16 +25712,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L225" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L225" s="5" t="n">
+        <v>0.1864</v>
       </c>
       <c r="M225" s="5" t="n">
-        <v>-0.008803999999999999</v>
+        <v>0.118909</v>
       </c>
       <c r="N225" s="5" t="n">
-        <v>-0.024924</v>
+        <v>0.0444</v>
       </c>
       <c r="O225" t="inlineStr">
         <is>
@@ -25779,15 +25745,19 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Government grant 7</t>
-        </is>
-      </c>
-      <c r="D226" t="inlineStr"/>
+          <t>Travel</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E226" t="inlineStr">
         <is>
           <t>-</t>
@@ -25808,31 +25778,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I226" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J226" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K226" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L226" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I226" s="5" t="n">
+        <v>0.119836</v>
+      </c>
+      <c r="J226" s="5" t="n">
+        <v>0.092081</v>
+      </c>
+      <c r="K226" s="5" t="n">
+        <v>0.09388000000000001</v>
+      </c>
+      <c r="L226" s="5" t="n">
+        <v>0.008085</v>
       </c>
       <c r="M226" s="5" t="n">
-        <v>0.001804</v>
+        <v>0.031962</v>
       </c>
       <c r="N226" s="5" t="n">
-        <v>0.022041</v>
+        <v>0.041514</v>
       </c>
       <c r="O226" t="inlineStr">
         <is>
@@ -25858,12 +25820,12 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Foreign currency loss</t>
+          <t>Promotion expenses</t>
         </is>
       </c>
       <c r="D227" t="inlineStr"/>
@@ -25892,28 +25854,22 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J227" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K227" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J227" s="5" t="n">
+        <v>0.011119</v>
+      </c>
+      <c r="K227" s="5" t="n">
+        <v>0.006</v>
       </c>
       <c r="L227" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="M227" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M227" s="5" t="n">
+        <v>0.047154</v>
       </c>
       <c r="N227" s="5" t="n">
-        <v>-0.004548</v>
+        <v>0.034846</v>
       </c>
       <c r="O227" t="inlineStr">
         <is>
@@ -25939,12 +25895,12 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Change in fair value of investments 4</t>
+          <t>Information technology</t>
         </is>
       </c>
       <c r="D228" t="inlineStr"/>
@@ -25989,10 +25945,10 @@
         </is>
       </c>
       <c r="M228" s="5" t="n">
-        <v>0.014898</v>
+        <v>0.068786</v>
       </c>
       <c r="N228" s="5" t="n">
-        <v>-0.113082</v>
+        <v>0.032091</v>
       </c>
       <c r="O228" t="inlineStr">
         <is>
@@ -26018,17 +25974,17 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss $</t>
+          <t>Amortization 5</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>Amortization</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
@@ -26066,16 +26022,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L229" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L229" s="5" t="n">
+        <v>0.022305</v>
       </c>
       <c r="M229" s="5" t="n">
-        <v>-1.562648</v>
+        <v>0.022305</v>
       </c>
       <c r="N229" s="5" t="n">
-        <v>-2.80457</v>
+        <v>0.022305</v>
       </c>
       <c r="O229" t="inlineStr">
         <is>
@@ -26101,17 +26055,17 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Basic and diluted loss per share $</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>BasicEPS</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
@@ -26134,31 +26088,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I230" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J230" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K230" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L230" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I230" s="5" t="n">
+        <v>0.010148</v>
+      </c>
+      <c r="J230" s="5" t="n">
+        <v>0.01377</v>
+      </c>
+      <c r="K230" s="5" t="n">
+        <v>0.01374</v>
+      </c>
+      <c r="L230" s="5" t="n">
+        <v>0.0145</v>
       </c>
       <c r="M230" s="5" t="n">
-        <v>1.5e-08</v>
+        <v>0.016399</v>
       </c>
       <c r="N230" s="5" t="n">
-        <v>2.1e-08</v>
+        <v>0.019683</v>
       </c>
       <c r="O230" t="inlineStr">
         <is>
@@ -26184,12 +26130,12 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>See accompanying notes to financial statements.   7</t>
+          <t>Other items</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Balance, December 31, 2021 14,012,838 - 10,173,156 - 506,603</t>
+          <t>Financial Income</t>
         </is>
       </c>
       <c r="D231" t="inlineStr"/>
@@ -26234,10 +26180,10 @@
         </is>
       </c>
       <c r="M231" s="5" t="n">
-        <v>2.711419</v>
+        <v>0.001265</v>
       </c>
       <c r="N231" s="5" t="n">
-        <v>-7.96834</v>
+        <v>0.07699499999999999</v>
       </c>
       <c r="O231" t="inlineStr">
         <is>
@@ -26263,12 +26209,12 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>See accompanying notes to financial statements.   7</t>
+          <t>Other items</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Share-based payments 8 - - - - 541,991</t>
+          <t>Financial expenses</t>
         </is>
       </c>
       <c r="D232" t="inlineStr"/>
@@ -26313,12 +26259,10 @@
         </is>
       </c>
       <c r="M232" s="5" t="n">
-        <v>0.541991</v>
-      </c>
-      <c r="N232" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.008803999999999999</v>
+      </c>
+      <c r="N232" s="5" t="n">
+        <v>-0.024924</v>
       </c>
       <c r="O232" t="inlineStr">
         <is>
@@ -26344,12 +26288,12 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>See accompanying notes to financial statements.   7</t>
+          <t>Other items</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Share issue costs - - 340 - -</t>
+          <t>Government grant 7</t>
         </is>
       </c>
       <c r="D233" t="inlineStr"/>
@@ -26394,12 +26338,10 @@
         </is>
       </c>
       <c r="M233" s="5" t="n">
-        <v>0.00034</v>
-      </c>
-      <c r="N233" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.001804</v>
+      </c>
+      <c r="N233" s="5" t="n">
+        <v>0.022041</v>
       </c>
       <c r="O233" t="inlineStr">
         <is>
@@ -26425,12 +26367,12 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>See accompanying notes to financial statements.   7</t>
+          <t>Other items</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Exercise of options 8 250,000 - 53,982 - (28,982)</t>
+          <t>Foreign currency loss</t>
         </is>
       </c>
       <c r="D234" t="inlineStr"/>
@@ -26474,13 +26416,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M234" s="5" t="n">
-        <v>0.025</v>
-      </c>
-      <c r="N234" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M234" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N234" s="5" t="n">
+        <v>-0.004548</v>
       </c>
       <c r="O234" t="inlineStr">
         <is>
@@ -26506,12 +26448,12 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>See accompanying notes to financial statements.   7</t>
+          <t>Other items</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Exercise of warrants 8 21,240,000 - 3,186,000 - -</t>
+          <t>Change in fair value of investments 4</t>
         </is>
       </c>
       <c r="D235" t="inlineStr"/>
@@ -26556,12 +26498,10 @@
         </is>
       </c>
       <c r="M235" s="5" t="n">
-        <v>3.186</v>
-      </c>
-      <c r="N235" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.014898</v>
+      </c>
+      <c r="N235" s="5" t="n">
+        <v>-0.113082</v>
       </c>
       <c r="O235" t="inlineStr">
         <is>
@@ -26587,12 +26527,12 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>See accompanying notes to financial statements.   7</t>
+          <t>Other items</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Net loss - - - - -</t>
+          <t>Net loss and comprehensive loss $</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -26641,7 +26581,7 @@
         </is>
       </c>
       <c r="M236" s="5" t="n">
-        <v>-2.80457</v>
+        <v>-1.562648</v>
       </c>
       <c r="N236" s="5" t="n">
         <v>-2.80457</v>
@@ -26670,15 +26610,19 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>See accompanying notes to financial statements.   7</t>
+          <t>Other items</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Balance as at December 31, 2022 135,502,838 - 13,413,478 - 1,019,612</t>
-        </is>
-      </c>
-      <c r="D237" t="inlineStr"/>
+          <t>Basic and diluted loss per share $</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E237" t="inlineStr">
         <is>
           <t>-</t>
@@ -26720,10 +26664,10 @@
         </is>
       </c>
       <c r="M237" s="5" t="n">
-        <v>3.66018</v>
+        <v>1.5e-08</v>
       </c>
       <c r="N237" s="5" t="n">
-        <v>-10.77291</v>
+        <v>2.1e-08</v>
       </c>
       <c r="O237" t="inlineStr">
         <is>
@@ -26754,7 +26698,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Balance as at December 31, 2020 60,527,838 250,000 6,334,571 12,500 280,404</t>
+          <t>Balance, December 31, 2021 14,012,838 - 10,173,156 - 506,603</t>
         </is>
       </c>
       <c r="D238" t="inlineStr"/>
@@ -26799,10 +26743,10 @@
         </is>
       </c>
       <c r="M238" s="5" t="n">
-        <v>0.221783</v>
+        <v>2.711419</v>
       </c>
       <c r="N238" s="5" t="n">
-        <v>-6.405692</v>
+        <v>-7.96834</v>
       </c>
       <c r="O238" t="inlineStr">
         <is>
@@ -26833,7 +26777,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Share-based payments 8 - - - 263,745</t>
+          <t>Share-based payments 8 - - - - 541,991</t>
         </is>
       </c>
       <c r="D239" t="inlineStr"/>
@@ -26878,7 +26822,7 @@
         </is>
       </c>
       <c r="M239" s="5" t="n">
-        <v>0.263745</v>
+        <v>0.541991</v>
       </c>
       <c r="N239" t="inlineStr">
         <is>
@@ -26914,7 +26858,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Units issued for private placement 8 40,000,000 (250,000) 2,000,000 (12,500) -</t>
+          <t>Share issue costs - - 340 - -</t>
         </is>
       </c>
       <c r="D240" t="inlineStr"/>
@@ -26959,7 +26903,7 @@
         </is>
       </c>
       <c r="M240" s="5" t="n">
-        <v>1.9875</v>
+        <v>0.00034</v>
       </c>
       <c r="N240" t="inlineStr">
         <is>
@@ -26995,7 +26939,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Share issue costs 8 - - (71,711) - -</t>
+          <t>Exercise of options 8 250,000 - 53,982 - (28,982)</t>
         </is>
       </c>
       <c r="D241" t="inlineStr"/>
@@ -27040,7 +26984,7 @@
         </is>
       </c>
       <c r="M241" s="5" t="n">
-        <v>-0.071711</v>
+        <v>0.025</v>
       </c>
       <c r="N241" t="inlineStr">
         <is>
@@ -27076,7 +27020,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Exercise of options 8 1,600,000 - 127,546 - (37,546)</t>
+          <t>Exercise of warrants 8 21,240,000 - 3,186,000 - -</t>
         </is>
       </c>
       <c r="D242" t="inlineStr"/>
@@ -27121,7 +27065,7 @@
         </is>
       </c>
       <c r="M242" s="5" t="n">
-        <v>0.09</v>
+        <v>3.186</v>
       </c>
       <c r="N242" t="inlineStr">
         <is>
@@ -27157,10 +27101,14 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Exercise of warrants 8 11,885,000 - 1,782,750 - -</t>
-        </is>
-      </c>
-      <c r="D243" t="inlineStr"/>
+          <t>Net loss - - - - -</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E243" t="inlineStr">
         <is>
           <t>-</t>
@@ -27202,12 +27150,10 @@
         </is>
       </c>
       <c r="M243" s="5" t="n">
-        <v>1.78275</v>
-      </c>
-      <c r="N243" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-2.80457</v>
+      </c>
+      <c r="N243" s="5" t="n">
+        <v>-2.80457</v>
       </c>
       <c r="O243" t="inlineStr">
         <is>
@@ -27238,7 +27184,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Balance as at December 31, 2021 114,012,838 - 10,173,156 - 506,603</t>
+          <t>Balance as at December 31, 2022 135,502,838 - 13,413,478 - 1,019,612</t>
         </is>
       </c>
       <c r="D244" t="inlineStr"/>
@@ -27283,10 +27229,10 @@
         </is>
       </c>
       <c r="M244" s="5" t="n">
-        <v>2.711419</v>
+        <v>3.66018</v>
       </c>
       <c r="N244" s="5" t="n">
-        <v>-7.96834</v>
+        <v>-10.77291</v>
       </c>
       <c r="O244" t="inlineStr">
         <is>
@@ -27312,12 +27258,12 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>See accompanying notes to financial statements.   7</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Financial expenses</t>
+          <t>Balance as at December 31, 2020 60,527,838 250,000 6,334,571 12,500 280,404</t>
         </is>
       </c>
       <c r="D245" t="inlineStr"/>
@@ -27356,16 +27302,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L245" s="5" t="n">
-        <v>0.003542</v>
+      <c r="L245" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M245" s="5" t="n">
-        <v>0.008803999999999999</v>
-      </c>
-      <c r="N245" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.221783</v>
+      </c>
+      <c r="N245" s="5" t="n">
+        <v>-6.405692</v>
       </c>
       <c r="O245" t="inlineStr">
         <is>
@@ -27391,12 +27337,12 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>Other income</t>
+          <t>See accompanying notes to financial statements.   7</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Financial Income</t>
+          <t>Share-based payments 8 - - - 263,745</t>
         </is>
       </c>
       <c r="D246" t="inlineStr"/>
@@ -27435,11 +27381,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L246" s="5" t="n">
-        <v>0.000236</v>
+      <c r="L246" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M246" s="5" t="n">
-        <v>0.001265</v>
+        <v>0.263745</v>
       </c>
       <c r="N246" t="inlineStr">
         <is>
@@ -27470,12 +27418,12 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>Other income</t>
+          <t>See accompanying notes to financial statements.   7</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Government grant 7</t>
+          <t>Units issued for private placement 8 40,000,000 (250,000) 2,000,000 (12,500) -</t>
         </is>
       </c>
       <c r="D247" t="inlineStr"/>
@@ -27514,11 +27462,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L247" s="5" t="n">
-        <v>0.010442</v>
+      <c r="L247" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M247" s="5" t="n">
-        <v>0.001804</v>
+        <v>1.9875</v>
       </c>
       <c r="N247" t="inlineStr">
         <is>
@@ -27549,12 +27499,12 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>Other income</t>
+          <t>See accompanying notes to financial statements.   7</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Change in fair value of investments</t>
+          <t>Share issue costs 8 - - (71,711) - -</t>
         </is>
       </c>
       <c r="D248" t="inlineStr"/>
@@ -27599,7 +27549,7 @@
         </is>
       </c>
       <c r="M248" s="5" t="n">
-        <v>0.014898</v>
+        <v>-0.071711</v>
       </c>
       <c r="N248" t="inlineStr">
         <is>
@@ -27630,12 +27580,12 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Other income</t>
+          <t>See accompanying notes to financial statements.   7</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Other income total</t>
+          <t>Exercise of options 8 1,600,000 - 127,546 - (37,546)</t>
         </is>
       </c>
       <c r="D249" t="inlineStr"/>
@@ -27664,17 +27614,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J249" s="5" t="n">
-        <v>0.008226000000000001</v>
-      </c>
-      <c r="K249" s="5" t="n">
-        <v>0.004434</v>
-      </c>
-      <c r="L249" s="5" t="n">
-        <v>0.010678</v>
+      <c r="J249" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K249" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L249" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M249" s="5" t="n">
-        <v>0.017967</v>
+        <v>0.09</v>
       </c>
       <c r="N249" t="inlineStr">
         <is>
@@ -27705,19 +27661,15 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Other income</t>
+          <t>See accompanying notes to financial statements.   7</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss $</t>
-        </is>
-      </c>
-      <c r="D250" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Exercise of warrants 8 11,885,000 - 1,782,750 - -</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr"/>
       <c r="E250" t="inlineStr">
         <is>
           <t>-</t>
@@ -27753,11 +27705,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L250" s="5" t="n">
-        <v>-0.799251</v>
+      <c r="L250" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M250" s="5" t="n">
-        <v>-1.562648</v>
+        <v>1.78275</v>
       </c>
       <c r="N250" t="inlineStr">
         <is>
@@ -27788,19 +27742,15 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Other income</t>
+          <t>See accompanying notes to financial statements.   7</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Basic and diluted loss per share $</t>
-        </is>
-      </c>
-      <c r="D251" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
+          <t>Balance as at December 31, 2021 114,012,838 - 10,173,156 - 506,603</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr"/>
       <c r="E251" t="inlineStr">
         <is>
           <t>-</t>
@@ -27836,16 +27786,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L251" s="5" t="n">
-        <v>1.3e-08</v>
+      <c r="L251" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M251" s="5" t="n">
-        <v>1.5e-08</v>
-      </c>
-      <c r="N251" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>2.711419</v>
+      </c>
+      <c r="N251" s="5" t="n">
+        <v>-7.96834</v>
       </c>
       <c r="O251" t="inlineStr">
         <is>
@@ -27871,12 +27821,12 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>See accompanying notes to financial statements.   6</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Balance, December 31, 2019 60,527,838 - 6,334,571 - 782,829</t>
+          <t>Financial expenses</t>
         </is>
       </c>
       <c r="D252" t="inlineStr"/>
@@ -27916,10 +27866,10 @@
         </is>
       </c>
       <c r="L252" s="5" t="n">
-        <v>0.893034</v>
+        <v>0.003542</v>
       </c>
       <c r="M252" s="5" t="n">
-        <v>-6.224366</v>
+        <v>0.008803999999999999</v>
       </c>
       <c r="N252" t="inlineStr">
         <is>
@@ -27950,12 +27900,12 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>See accompanying notes to financial statements.   6</t>
+          <t>Other income</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Share-based payments 8 - - - - 115,500</t>
+          <t>Financial Income</t>
         </is>
       </c>
       <c r="D253" t="inlineStr"/>
@@ -27995,12 +27945,10 @@
         </is>
       </c>
       <c r="L253" s="5" t="n">
-        <v>0.1155</v>
-      </c>
-      <c r="M253" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.000236</v>
+      </c>
+      <c r="M253" s="5" t="n">
+        <v>0.001265</v>
       </c>
       <c r="N253" t="inlineStr">
         <is>
@@ -28031,12 +27979,12 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>See accompanying notes to financial statements.   6</t>
+          <t>Other income</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Units issued for private placement 8 - 250,000 - 12,500 -</t>
+          <t>Government grant 7</t>
         </is>
       </c>
       <c r="D254" t="inlineStr"/>
@@ -28076,12 +28024,10 @@
         </is>
       </c>
       <c r="L254" s="5" t="n">
-        <v>0.0125</v>
-      </c>
-      <c r="M254" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.010442</v>
+      </c>
+      <c r="M254" s="5" t="n">
+        <v>0.001804</v>
       </c>
       <c r="N254" t="inlineStr">
         <is>
@@ -28112,12 +28058,12 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>See accompanying notes to financial statements.   6</t>
+          <t>Other income</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Expiry of options 8 - - - - (617,925)</t>
+          <t>Change in fair value of investments</t>
         </is>
       </c>
       <c r="D255" t="inlineStr"/>
@@ -28162,7 +28108,7 @@
         </is>
       </c>
       <c r="M255" s="5" t="n">
-        <v>0.6179249999999999</v>
+        <v>0.014898</v>
       </c>
       <c r="N255" t="inlineStr">
         <is>
@@ -28193,19 +28139,15 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>See accompanying notes to financial statements.   6</t>
+          <t>Other income</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Net loss - - - - -</t>
-        </is>
-      </c>
-      <c r="D256" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Other income total</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr"/>
       <c r="E256" t="inlineStr">
         <is>
           <t>-</t>
@@ -28231,21 +28173,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J256" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K256" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J256" s="5" t="n">
+        <v>0.008226000000000001</v>
+      </c>
+      <c r="K256" s="5" t="n">
+        <v>0.004434</v>
       </c>
       <c r="L256" s="5" t="n">
-        <v>-0.799251</v>
+        <v>0.010678</v>
       </c>
       <c r="M256" s="5" t="n">
-        <v>-0.799251</v>
+        <v>0.017967</v>
       </c>
       <c r="N256" t="inlineStr">
         <is>
@@ -28276,15 +28214,19 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>See accompanying notes to financial statements.   6</t>
+          <t>Other income</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Balance, December 31, 2020 60,527,838 250,000 6,334,571 12,500 280,404</t>
-        </is>
-      </c>
-      <c r="D257" t="inlineStr"/>
+          <t>Net loss and comprehensive loss $</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E257" t="inlineStr">
         <is>
           <t>-</t>
@@ -28321,10 +28263,10 @@
         </is>
       </c>
       <c r="L257" s="5" t="n">
-        <v>0.221783</v>
+        <v>-0.799251</v>
       </c>
       <c r="M257" s="5" t="n">
-        <v>-6.405692</v>
+        <v>-1.562648</v>
       </c>
       <c r="N257" t="inlineStr">
         <is>
@@ -28355,15 +28297,19 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>See accompanying notes to financial statements.   6</t>
+          <t>Other income</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Share-based payments 8 - - - - 263,745</t>
-        </is>
-      </c>
-      <c r="D258" t="inlineStr"/>
+          <t>Basic and diluted loss per share $</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E258" t="inlineStr">
         <is>
           <t>-</t>
@@ -28400,12 +28346,10 @@
         </is>
       </c>
       <c r="L258" s="5" t="n">
-        <v>0.263745</v>
-      </c>
-      <c r="M258" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1.3e-08</v>
+      </c>
+      <c r="M258" s="5" t="n">
+        <v>1.5e-08</v>
       </c>
       <c r="N258" t="inlineStr">
         <is>
@@ -28441,7 +28385,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Units issued for private placement 8 40,000,000 (250,000) 2,000,000 (12,500) -</t>
+          <t>Balance, December 31, 2019 60,527,838 - 6,334,571 - 782,829</t>
         </is>
       </c>
       <c r="D259" t="inlineStr"/>
@@ -28481,12 +28425,10 @@
         </is>
       </c>
       <c r="L259" s="5" t="n">
-        <v>1.9875</v>
-      </c>
-      <c r="M259" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.893034</v>
+      </c>
+      <c r="M259" s="5" t="n">
+        <v>-6.224366</v>
       </c>
       <c r="N259" t="inlineStr">
         <is>
@@ -28522,7 +28464,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Share issue costs 8 - - (71,711) - -</t>
+          <t>Share-based payments 8 - - - - 115,500</t>
         </is>
       </c>
       <c r="D260" t="inlineStr"/>
@@ -28562,7 +28504,7 @@
         </is>
       </c>
       <c r="L260" s="5" t="n">
-        <v>-0.071711</v>
+        <v>0.1155</v>
       </c>
       <c r="M260" t="inlineStr">
         <is>
@@ -28603,7 +28545,7 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Exercise of options 8 1,600,000 - 127,546 - (37,546)</t>
+          <t>Units issued for private placement 8 - 250,000 - 12,500 -</t>
         </is>
       </c>
       <c r="D261" t="inlineStr"/>
@@ -28643,7 +28585,7 @@
         </is>
       </c>
       <c r="L261" s="5" t="n">
-        <v>0.09</v>
+        <v>0.0125</v>
       </c>
       <c r="M261" t="inlineStr">
         <is>
@@ -28684,7 +28626,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Exercise of warrants 8 11,885,000 - 1,782,750 - -</t>
+          <t>Expiry of options 8 - - - - (617,925)</t>
         </is>
       </c>
       <c r="D262" t="inlineStr"/>
@@ -28723,13 +28665,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L262" s="5" t="n">
-        <v>1.78275</v>
-      </c>
-      <c r="M262" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L262" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M262" s="5" t="n">
+        <v>0.6179249999999999</v>
       </c>
       <c r="N262" t="inlineStr">
         <is>
@@ -28765,10 +28707,14 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Balance, December 31, 2021 114,012,838 - 10,173,156 - 506,603</t>
-        </is>
-      </c>
-      <c r="D263" t="inlineStr"/>
+          <t>Net loss - - - - -</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E263" t="inlineStr">
         <is>
           <t>-</t>
@@ -28805,10 +28751,10 @@
         </is>
       </c>
       <c r="L263" s="5" t="n">
-        <v>2.711419</v>
+        <v>-0.799251</v>
       </c>
       <c r="M263" s="5" t="n">
-        <v>-7.96834</v>
+        <v>-0.799251</v>
       </c>
       <c r="N263" t="inlineStr">
         <is>
@@ -28839,12 +28785,12 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>See accompanying notes to financial statements.   6</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Salaries 10</t>
+          <t>Balance, December 31, 2020 60,527,838 250,000 6,334,571 12,500 280,404</t>
         </is>
       </c>
       <c r="D264" t="inlineStr"/>
@@ -28873,21 +28819,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J264" s="5" t="n">
-        <v>0.327569</v>
-      </c>
-      <c r="K264" s="5" t="n">
-        <v>0.328638</v>
-      </c>
-      <c r="L264" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M264" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J264" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K264" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L264" s="5" t="n">
+        <v>0.221783</v>
+      </c>
+      <c r="M264" s="5" t="n">
+        <v>-6.405692</v>
       </c>
       <c r="N264" t="inlineStr">
         <is>
@@ -28918,12 +28864,12 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>See accompanying notes to financial statements.   6</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Development costs</t>
+          <t>Share-based payments 8 - - - - 263,745</t>
         </is>
       </c>
       <c r="D265" t="inlineStr"/>
@@ -28947,19 +28893,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I265" s="5" t="n">
-        <v>0.084856</v>
-      </c>
-      <c r="J265" s="5" t="n">
-        <v>0.107579</v>
-      </c>
-      <c r="K265" s="5" t="n">
-        <v>0.084034</v>
-      </c>
-      <c r="L265" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I265" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J265" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K265" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L265" s="5" t="n">
+        <v>0.263745</v>
       </c>
       <c r="M265" t="inlineStr">
         <is>
@@ -28995,12 +28945,12 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>See accompanying notes to financial statements.   6</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Legal and audit fees</t>
+          <t>Units issued for private placement 8 40,000,000 (250,000) 2,000,000 (12,500) -</t>
         </is>
       </c>
       <c r="D266" t="inlineStr"/>
@@ -29029,16 +28979,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J266" s="5" t="n">
-        <v>0.061465</v>
-      </c>
-      <c r="K266" s="5" t="n">
-        <v>0.042052</v>
-      </c>
-      <c r="L266" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J266" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K266" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L266" s="5" t="n">
+        <v>1.9875</v>
       </c>
       <c r="M266" t="inlineStr">
         <is>
@@ -29074,12 +29026,12 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>See accompanying notes to financial statements.   6</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Share-based payments 9,10</t>
+          <t>Share issue costs 8 - - (71,711) - -</t>
         </is>
       </c>
       <c r="D267" t="inlineStr"/>
@@ -29108,16 +29060,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J267" s="5" t="n">
-        <v>0.140016</v>
-      </c>
-      <c r="K267" s="5" t="n">
-        <v>0.020074</v>
-      </c>
-      <c r="L267" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J267" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K267" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L267" s="5" t="n">
+        <v>-0.071711</v>
       </c>
       <c r="M267" t="inlineStr">
         <is>
@@ -29153,19 +29107,15 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>See accompanying notes to financial statements.   6</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Amortization 6</t>
-        </is>
-      </c>
-      <c r="D268" t="inlineStr">
-        <is>
-          <t>Amortization</t>
-        </is>
-      </c>
+          <t>Exercise of options 8 1,600,000 - 127,546 - (37,546)</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr"/>
       <c r="E268" t="inlineStr">
         <is>
           <t>-</t>
@@ -29196,13 +29146,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K268" s="5" t="n">
-        <v>0.005194</v>
-      </c>
-      <c r="L268" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K268" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L268" s="5" t="n">
+        <v>0.09</v>
       </c>
       <c r="M268" t="inlineStr">
         <is>
@@ -29238,19 +29188,15 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>See accompanying notes to financial statements.   6</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Consulting fees 10</t>
-        </is>
-      </c>
-      <c r="D269" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Exercise of warrants 8 11,885,000 - 1,782,750 - -</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr"/>
       <c r="E269" t="inlineStr">
         <is>
           <t>-</t>
@@ -29276,16 +29222,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J269" s="5" t="n">
-        <v>0.031282</v>
-      </c>
-      <c r="K269" s="5" t="n">
-        <v>0.0032</v>
-      </c>
-      <c r="L269" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J269" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K269" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L269" s="5" t="n">
+        <v>1.78275</v>
       </c>
       <c r="M269" t="inlineStr">
         <is>
@@ -29321,19 +29269,15 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>See accompanying notes to financial statements.   6</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Interest and bank charges</t>
-        </is>
-      </c>
-      <c r="D270" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Balance, December 31, 2021 114,012,838 - 10,173,156 - 506,603</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr"/>
       <c r="E270" t="inlineStr">
         <is>
           <t>-</t>
@@ -29354,24 +29298,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I270" s="5" t="n">
-        <v>0.000695</v>
-      </c>
-      <c r="J270" s="5" t="n">
-        <v>0.000621</v>
-      </c>
-      <c r="K270" s="5" t="n">
-        <v>0.000629</v>
-      </c>
-      <c r="L270" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M270" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I270" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J270" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K270" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L270" s="5" t="n">
+        <v>2.711419</v>
+      </c>
+      <c r="M270" s="5" t="n">
+        <v>-7.96834</v>
       </c>
       <c r="N270" t="inlineStr">
         <is>
@@ -29402,12 +29348,12 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Other Expenses</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Exploration and evaluation expenses</t>
+          <t>Salaries 10</t>
         </is>
       </c>
       <c r="D271" t="inlineStr"/>
@@ -29437,12 +29383,10 @@
         </is>
       </c>
       <c r="J271" s="5" t="n">
-        <v>0.00312</v>
-      </c>
-      <c r="K271" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.327569</v>
+      </c>
+      <c r="K271" s="5" t="n">
+        <v>0.328638</v>
       </c>
       <c r="L271" t="inlineStr">
         <is>
@@ -29483,12 +29427,12 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Change in fair value of financial assets and</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Change in fair value of financial assets and liabilities at fair value through profit or loss</t>
+          <t>Development costs</t>
         </is>
       </c>
       <c r="D272" t="inlineStr"/>
@@ -29513,15 +29457,13 @@
         </is>
       </c>
       <c r="I272" s="5" t="n">
-        <v>-0.145</v>
+        <v>0.084856</v>
       </c>
       <c r="J272" s="5" t="n">
-        <v>0.048155</v>
-      </c>
-      <c r="K272" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.107579</v>
+      </c>
+      <c r="K272" s="5" t="n">
+        <v>0.084034</v>
       </c>
       <c r="L272" t="inlineStr">
         <is>
@@ -29562,12 +29504,12 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>Change in fair value of financial assets and</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Loss on advance receivable</t>
+          <t>Legal and audit fees</t>
         </is>
       </c>
       <c r="D273" t="inlineStr"/>
@@ -29597,12 +29539,10 @@
         </is>
       </c>
       <c r="J273" s="5" t="n">
-        <v>0.00107</v>
-      </c>
-      <c r="K273" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.061465</v>
+      </c>
+      <c r="K273" s="5" t="n">
+        <v>0.042052</v>
       </c>
       <c r="L273" t="inlineStr">
         <is>
@@ -29643,12 +29583,12 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>Change in fair value of financial assets and</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Change in fair value of financial assets and total</t>
+          <t>Share-based payments 9,10</t>
         </is>
       </c>
       <c r="D274" t="inlineStr"/>
@@ -29672,16 +29612,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I274" s="5" t="n">
-        <v>-0.172462</v>
+      <c r="I274" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J274" s="5" t="n">
-        <v>0.052345</v>
-      </c>
-      <c r="K274" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.140016</v>
+      </c>
+      <c r="K274" s="5" t="n">
+        <v>0.020074</v>
       </c>
       <c r="L274" t="inlineStr">
         <is>
@@ -29722,17 +29662,17 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>Other income</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Interest Income</t>
+          <t>Amortization 6</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>InterestIncomeNonOperating</t>
+          <t>Amortization</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
@@ -29760,11 +29700,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J275" s="5" t="n">
-        <v>0.008226000000000001</v>
+      <c r="J275" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K275" s="5" t="n">
-        <v>0.004433</v>
+        <v>0.005194</v>
       </c>
       <c r="L275" t="inlineStr">
         <is>
@@ -29805,15 +29747,19 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>Other income</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Gain on disposal of mineral properties</t>
-        </is>
-      </c>
-      <c r="D276" t="inlineStr"/>
+          <t>Consulting fees 10</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E276" t="inlineStr">
         <is>
           <t>-</t>
@@ -29839,13 +29785,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J276" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J276" s="5" t="n">
+        <v>0.031282</v>
       </c>
       <c r="K276" s="5" t="n">
-        <v>1e-06</v>
+        <v>0.0032</v>
       </c>
       <c r="L276" t="inlineStr">
         <is>
@@ -29886,17 +29830,17 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>Other income</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss for the year</t>
+          <t>Interest and bank charges</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
@@ -29919,16 +29863,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I277" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I277" s="5" t="n">
+        <v>0.000695</v>
       </c>
       <c r="J277" s="5" t="n">
-        <v>-0.916042</v>
+        <v>0.000621</v>
       </c>
       <c r="K277" s="5" t="n">
-        <v>-0.663318</v>
+        <v>0.000629</v>
       </c>
       <c r="L277" t="inlineStr">
         <is>
@@ -29969,19 +29911,15 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Other income</t>
+          <t>Other Expenses</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Basic and diluted loss per share 8</t>
-        </is>
-      </c>
-      <c r="D278" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
+          <t>Exploration and evaluation expenses</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr"/>
       <c r="E278" t="inlineStr">
         <is>
           <t>-</t>
@@ -30008,10 +29946,12 @@
         </is>
       </c>
       <c r="J278" s="5" t="n">
-        <v>2e-08</v>
-      </c>
-      <c r="K278" s="5" t="n">
-        <v>1e-08</v>
+        <v>0.00312</v>
+      </c>
+      <c r="K278" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L278" t="inlineStr">
         <is>
@@ -30052,12 +29992,12 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Notes</t>
+          <t>Change in fair value of financial assets and</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Balance, December 31, 2017 55,560,838 5,837,871 682,769</t>
+          <t>Change in fair value of financial assets and liabilities at fair value through profit or loss</t>
         </is>
       </c>
       <c r="D279" t="inlineStr"/>
@@ -30082,13 +30022,15 @@
         </is>
       </c>
       <c r="I279" s="5" t="n">
-        <v>1.815604</v>
+        <v>-0.145</v>
       </c>
       <c r="J279" s="5" t="n">
-        <v>1.815604</v>
-      </c>
-      <c r="K279" s="5" t="n">
-        <v>-4.705036</v>
+        <v>0.048155</v>
+      </c>
+      <c r="K279" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L279" t="inlineStr">
         <is>
@@ -30129,12 +30071,12 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Notes</t>
+          <t>Change in fair value of financial assets and</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Share-based payments 9 - - 140,016</t>
+          <t>Loss on advance receivable</t>
         </is>
       </c>
       <c r="D280" t="inlineStr"/>
@@ -30164,7 +30106,7 @@
         </is>
       </c>
       <c r="J280" s="5" t="n">
-        <v>0.140016</v>
+        <v>0.00107</v>
       </c>
       <c r="K280" t="inlineStr">
         <is>
@@ -30210,12 +30152,12 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Notes</t>
+          <t>Change in fair value of financial assets and</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Exercise of warrants 9 4,967,000 496,700 -</t>
+          <t>Change in fair value of financial assets and total</t>
         </is>
       </c>
       <c r="D281" t="inlineStr"/>
@@ -30239,13 +30181,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I281" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I281" s="5" t="n">
+        <v>-0.172462</v>
       </c>
       <c r="J281" s="5" t="n">
-        <v>0.4967</v>
+        <v>0.052345</v>
       </c>
       <c r="K281" t="inlineStr">
         <is>
@@ -30291,15 +30231,19 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Notes</t>
+          <t>Other income</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Expiry of options 9 - - (21,705)</t>
-        </is>
-      </c>
-      <c r="D282" t="inlineStr"/>
+          <t>Interest Income</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>InterestIncomeNonOperating</t>
+        </is>
+      </c>
       <c r="E282" t="inlineStr">
         <is>
           <t>-</t>
@@ -30325,13 +30269,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J282" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J282" s="5" t="n">
+        <v>0.008226000000000001</v>
       </c>
       <c r="K282" s="5" t="n">
-        <v>0.021705</v>
+        <v>0.004433</v>
       </c>
       <c r="L282" t="inlineStr">
         <is>
@@ -30372,12 +30314,12 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Notes</t>
+          <t>Other income</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Net loss for year - - -</t>
+          <t>Gain on disposal of mineral properties</t>
         </is>
       </c>
       <c r="D283" t="inlineStr"/>
@@ -30401,14 +30343,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I283" s="5" t="n">
-        <v>-1.431441</v>
-      </c>
-      <c r="J283" s="5" t="n">
-        <v>-0.916042</v>
+      <c r="I283" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J283" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K283" s="5" t="n">
-        <v>-0.916042</v>
+        <v>1e-06</v>
       </c>
       <c r="L283" t="inlineStr">
         <is>
@@ -30449,15 +30395,19 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Notes</t>
+          <t>Other income</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Balance, December 31, 2018 60,527,838 6,334,571 801,080</t>
-        </is>
-      </c>
-      <c r="D284" t="inlineStr"/>
+          <t>Net loss and comprehensive loss for the year</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E284" t="inlineStr">
         <is>
           <t>-</t>
@@ -30478,14 +30428,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I284" s="5" t="n">
-        <v>1.536278</v>
+      <c r="I284" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J284" s="5" t="n">
-        <v>1.536278</v>
+        <v>-0.916042</v>
       </c>
       <c r="K284" s="5" t="n">
-        <v>-5.599373</v>
+        <v>-0.663318</v>
       </c>
       <c r="L284" t="inlineStr">
         <is>
@@ -30526,15 +30478,19 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>Notes</t>
+          <t>Other income</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Share-based payments 9 - - 20,074</t>
-        </is>
-      </c>
-      <c r="D285" t="inlineStr"/>
+          <t>Basic and diluted loss per share 8</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E285" t="inlineStr">
         <is>
           <t>-</t>
@@ -30561,12 +30517,10 @@
         </is>
       </c>
       <c r="J285" s="5" t="n">
-        <v>0.020074</v>
-      </c>
-      <c r="K285" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>2e-08</v>
+      </c>
+      <c r="K285" s="5" t="n">
+        <v>1e-08</v>
       </c>
       <c r="L285" t="inlineStr">
         <is>
@@ -30612,7 +30566,7 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Expiry of options 9 - - (38,325)</t>
+          <t>Balance, December 31, 2017 55,560,838 5,837,871 682,769</t>
         </is>
       </c>
       <c r="D286" t="inlineStr"/>
@@ -30636,18 +30590,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I286" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J286" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I286" s="5" t="n">
+        <v>1.815604</v>
+      </c>
+      <c r="J286" s="5" t="n">
+        <v>1.815604</v>
       </c>
       <c r="K286" s="5" t="n">
-        <v>0.038325</v>
+        <v>-4.705036</v>
       </c>
       <c r="L286" t="inlineStr">
         <is>
@@ -30693,7 +30643,7 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Balance, December 31, 2019 60,527,838 6,334,571 782,829</t>
+          <t>Share-based payments 9 - - 140,016</t>
         </is>
       </c>
       <c r="D287" t="inlineStr"/>
@@ -30723,10 +30673,12 @@
         </is>
       </c>
       <c r="J287" s="5" t="n">
-        <v>0.893034</v>
-      </c>
-      <c r="K287" s="5" t="n">
-        <v>-6.224366</v>
+        <v>0.140016</v>
+      </c>
+      <c r="K287" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L287" t="inlineStr">
         <is>
@@ -30767,12 +30719,12 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Notes</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Salaries 11</t>
+          <t>Exercise of warrants 9 4,967,000 496,700 -</t>
         </is>
       </c>
       <c r="D288" t="inlineStr"/>
@@ -30796,11 +30748,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I288" s="5" t="n">
-        <v>0.390665</v>
+      <c r="I288" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J288" s="5" t="n">
-        <v>0.327569</v>
+        <v>0.4967</v>
       </c>
       <c r="K288" t="inlineStr">
         <is>
@@ -30846,12 +30800,12 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Notes</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Share-based payments 10, 11</t>
+          <t>Expiry of options 9 - - (21,705)</t>
         </is>
       </c>
       <c r="D289" t="inlineStr"/>
@@ -30875,16 +30829,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I289" s="5" t="n">
-        <v>0.661385</v>
-      </c>
-      <c r="J289" s="5" t="n">
-        <v>0.140016</v>
-      </c>
-      <c r="K289" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I289" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J289" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K289" s="5" t="n">
+        <v>0.021705</v>
       </c>
       <c r="L289" t="inlineStr">
         <is>
@@ -30925,12 +30881,12 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Notes</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Legal and audit fees 11</t>
+          <t>Net loss for year - - -</t>
         </is>
       </c>
       <c r="D290" t="inlineStr"/>
@@ -30955,15 +30911,13 @@
         </is>
       </c>
       <c r="I290" s="5" t="n">
-        <v>0.067298</v>
+        <v>-1.431441</v>
       </c>
       <c r="J290" s="5" t="n">
-        <v>0.061465</v>
-      </c>
-      <c r="K290" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.916042</v>
+      </c>
+      <c r="K290" s="5" t="n">
+        <v>-0.916042</v>
       </c>
       <c r="L290" t="inlineStr">
         <is>
@@ -31004,19 +30958,15 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Notes</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Consulting fees 11</t>
-        </is>
-      </c>
-      <c r="D291" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Balance, December 31, 2018 60,527,838 6,334,571 801,080</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr"/>
       <c r="E291" t="inlineStr">
         <is>
           <t>-</t>
@@ -31038,15 +30988,13 @@
         </is>
       </c>
       <c r="I291" s="5" t="n">
-        <v>0.177736</v>
+        <v>1.536278</v>
       </c>
       <c r="J291" s="5" t="n">
-        <v>0.031282</v>
-      </c>
-      <c r="K291" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1.536278</v>
+      </c>
+      <c r="K291" s="5" t="n">
+        <v>-5.599373</v>
       </c>
       <c r="L291" t="inlineStr">
         <is>
@@ -31087,12 +31035,12 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>Gain on disposal of exploration and evaluation</t>
+          <t>Notes</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Gain on disposal of exploration and evaluation assets 5</t>
+          <t>Share-based payments 9 - - 20,074</t>
         </is>
       </c>
       <c r="D292" t="inlineStr"/>
@@ -31116,13 +31064,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I292" s="5" t="n">
-        <v>-0.0275</v>
-      </c>
-      <c r="J292" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I292" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J292" s="5" t="n">
+        <v>0.020074</v>
       </c>
       <c r="K292" t="inlineStr">
         <is>
@@ -31168,12 +31116,12 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>Gain on disposal of exploration and evaluation</t>
+          <t>Notes</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Exploration and evaluation expenses</t>
+          <t>Expiry of options 9 - - (38,325)</t>
         </is>
       </c>
       <c r="D293" t="inlineStr"/>
@@ -31202,13 +31150,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J293" s="5" t="n">
-        <v>0.00312</v>
-      </c>
-      <c r="K293" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J293" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K293" s="5" t="n">
+        <v>0.038325</v>
       </c>
       <c r="L293" t="inlineStr">
         <is>
@@ -31249,12 +31197,12 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>Change in fair value of financial assets and</t>
+          <t>Notes</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Loss on advance receivable 11</t>
+          <t>Balance, December 31, 2019 60,527,838 6,334,571 782,829</t>
         </is>
       </c>
       <c r="D294" t="inlineStr"/>
@@ -31278,16 +31226,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I294" s="5" t="n">
-        <v>3.8e-05</v>
+      <c r="I294" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J294" s="5" t="n">
-        <v>0.00107</v>
-      </c>
-      <c r="K294" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.893034</v>
+      </c>
+      <c r="K294" s="5" t="n">
+        <v>-6.224366</v>
       </c>
       <c r="L294" t="inlineStr">
         <is>
@@ -31328,19 +31276,15 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>Change in fair value of financial assets and</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Interest Income</t>
-        </is>
-      </c>
-      <c r="D295" t="inlineStr">
-        <is>
-          <t>InterestIncomeNonOperating</t>
-        </is>
-      </c>
+          <t>Salaries 11</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr"/>
       <c r="E295" t="inlineStr">
         <is>
           <t>-</t>
@@ -31362,10 +31306,10 @@
         </is>
       </c>
       <c r="I295" s="5" t="n">
-        <v>0.004272</v>
+        <v>0.390665</v>
       </c>
       <c r="J295" s="5" t="n">
-        <v>0.008226000000000001</v>
+        <v>0.327569</v>
       </c>
       <c r="K295" t="inlineStr">
         <is>
@@ -31411,19 +31355,15 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>Change in fair value of financial assets and</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss for the year</t>
-        </is>
-      </c>
-      <c r="D296" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Share-based payments 10, 11</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr"/>
       <c r="E296" t="inlineStr">
         <is>
           <t>-</t>
@@ -31445,10 +31385,10 @@
         </is>
       </c>
       <c r="I296" s="5" t="n">
-        <v>-1.431441</v>
+        <v>0.661385</v>
       </c>
       <c r="J296" s="5" t="n">
-        <v>-0.916042</v>
+        <v>0.140016</v>
       </c>
       <c r="K296" t="inlineStr">
         <is>
@@ -31494,19 +31434,15 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>Change in fair value of financial assets and</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Basic and diluted loss per share 9</t>
-        </is>
-      </c>
-      <c r="D297" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
+          <t>Legal and audit fees 11</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr"/>
       <c r="E297" t="inlineStr">
         <is>
           <t>-</t>
@@ -31528,10 +31464,10 @@
         </is>
       </c>
       <c r="I297" s="5" t="n">
-        <v>3e-08</v>
+        <v>0.067298</v>
       </c>
       <c r="J297" s="5" t="n">
-        <v>2e-08</v>
+        <v>0.061465</v>
       </c>
       <c r="K297" t="inlineStr">
         <is>
@@ -31577,15 +31513,19 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>Notes</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Balance, December 31, 2016 43,369,338 4,608,618 93,219</t>
-        </is>
-      </c>
-      <c r="D298" t="inlineStr"/>
+          <t>Consulting fees 11</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E298" t="inlineStr">
         <is>
           <t>-</t>
@@ -31607,10 +31547,10 @@
         </is>
       </c>
       <c r="I298" s="5" t="n">
-        <v>1.36651</v>
+        <v>0.177736</v>
       </c>
       <c r="J298" s="5" t="n">
-        <v>-3.335327</v>
+        <v>0.031282</v>
       </c>
       <c r="K298" t="inlineStr">
         <is>
@@ -31656,12 +31596,12 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>Notes</t>
+          <t>Gain on disposal of exploration and evaluation</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Share-based payments 10 - - 661,385</t>
+          <t>Gain on disposal of exploration and evaluation assets 5</t>
         </is>
       </c>
       <c r="D299" t="inlineStr"/>
@@ -31686,7 +31626,7 @@
         </is>
       </c>
       <c r="I299" s="5" t="n">
-        <v>0.661385</v>
+        <v>-0.0275</v>
       </c>
       <c r="J299" t="inlineStr">
         <is>
@@ -31737,12 +31677,12 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>Notes</t>
+          <t>Gain on disposal of exploration and evaluation</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Exercise of warrants 10 11,991,500 1,199,707 (557)</t>
+          <t>Exploration and evaluation expenses</t>
         </is>
       </c>
       <c r="D300" t="inlineStr"/>
@@ -31766,13 +31706,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I300" s="5" t="n">
-        <v>1.19915</v>
-      </c>
-      <c r="J300" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I300" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J300" s="5" t="n">
+        <v>0.00312</v>
       </c>
       <c r="K300" t="inlineStr">
         <is>
@@ -31818,12 +31758,12 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>Notes</t>
+          <t>Change in fair value of financial assets and</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>Exercise of options 10 200,000 29,546 (9,546)</t>
+          <t>Loss on advance receivable 11</t>
         </is>
       </c>
       <c r="D301" t="inlineStr"/>
@@ -31848,12 +31788,10 @@
         </is>
       </c>
       <c r="I301" s="5" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="J301" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>3.8e-05</v>
+      </c>
+      <c r="J301" s="5" t="n">
+        <v>0.00107</v>
       </c>
       <c r="K301" t="inlineStr">
         <is>
@@ -31899,15 +31837,19 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>Notes</t>
+          <t>Change in fair value of financial assets and</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Transfer from options reserves on expiry of options - - (61,732)</t>
-        </is>
-      </c>
-      <c r="D302" t="inlineStr"/>
+          <t>Interest Income</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>InterestIncomeNonOperating</t>
+        </is>
+      </c>
       <c r="E302" t="inlineStr">
         <is>
           <t>-</t>
@@ -31928,13 +31870,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I302" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I302" s="5" t="n">
+        <v>0.004272</v>
       </c>
       <c r="J302" s="5" t="n">
-        <v>0.061732</v>
+        <v>0.008226000000000001</v>
       </c>
       <c r="K302" t="inlineStr">
         <is>
@@ -31980,15 +31920,19 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>Notes</t>
+          <t>Change in fair value of financial assets and</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>Share-based payments 10 - - 140,016</t>
-        </is>
-      </c>
-      <c r="D303" t="inlineStr"/>
+          <t>Net loss and comprehensive loss for the year</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E303" t="inlineStr">
         <is>
           <t>-</t>
@@ -32010,12 +31954,10 @@
         </is>
       </c>
       <c r="I303" s="5" t="n">
-        <v>0.140016</v>
-      </c>
-      <c r="J303" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-1.431441</v>
+      </c>
+      <c r="J303" s="5" t="n">
+        <v>-0.916042</v>
       </c>
       <c r="K303" t="inlineStr">
         <is>
@@ -32061,15 +32003,19 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>Notes</t>
+          <t>Change in fair value of financial assets and</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Exercise of warrants 10 4,967,000 496,700 -</t>
-        </is>
-      </c>
-      <c r="D304" t="inlineStr"/>
+          <t>Basic and diluted loss per share 9</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E304" t="inlineStr">
         <is>
           <t>-</t>
@@ -32091,12 +32037,10 @@
         </is>
       </c>
       <c r="I304" s="5" t="n">
-        <v>0.4967</v>
-      </c>
-      <c r="J304" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>3e-08</v>
+      </c>
+      <c r="J304" s="5" t="n">
+        <v>2e-08</v>
       </c>
       <c r="K304" t="inlineStr">
         <is>
@@ -32147,7 +32091,7 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>Expiry of options - - (21,705)</t>
+          <t>Balance, December 31, 2016 43,369,338 4,608,618 93,219</t>
         </is>
       </c>
       <c r="D305" t="inlineStr"/>
@@ -32171,45 +32115,610 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I305" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I305" s="5" t="n">
+        <v>1.36651</v>
       </c>
       <c r="J305" s="5" t="n">
+        <v>-3.335327</v>
+      </c>
+      <c r="K305" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L305" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M305" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N305" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O305" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P305" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q305" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>Share-based payments 10 - - 661,385</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr"/>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F306" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G306" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H306" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I306" s="5" t="n">
+        <v>0.661385</v>
+      </c>
+      <c r="J306" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K306" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L306" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M306" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N306" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O306" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P306" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q306" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>Exercise of warrants 10 11,991,500 1,199,707 (557)</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr"/>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F307" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G307" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H307" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I307" s="5" t="n">
+        <v>1.19915</v>
+      </c>
+      <c r="J307" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K307" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L307" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M307" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N307" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O307" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P307" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q307" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>Exercise of options 10 200,000 29,546 (9,546)</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr"/>
+      <c r="E308" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F308" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G308" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H308" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I308" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="J308" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K308" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L308" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M308" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N308" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O308" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P308" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q308" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>Transfer from options reserves on expiry of options - - (61,732)</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr"/>
+      <c r="E309" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F309" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G309" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H309" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I309" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J309" s="5" t="n">
+        <v>0.061732</v>
+      </c>
+      <c r="K309" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L309" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M309" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N309" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O309" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P309" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q309" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>Share-based payments 10 - - 140,016</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr"/>
+      <c r="E310" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F310" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G310" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H310" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I310" s="5" t="n">
+        <v>0.140016</v>
+      </c>
+      <c r="J310" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K310" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L310" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M310" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N310" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O310" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P310" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q310" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>Exercise of warrants 10 4,967,000 496,700 -</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr"/>
+      <c r="E311" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F311" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G311" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H311" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I311" s="5" t="n">
+        <v>0.4967</v>
+      </c>
+      <c r="J311" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K311" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L311" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M311" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N311" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O311" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P311" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q311" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>Expiry of options - - (21,705)</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr"/>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F312" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G312" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H312" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I312" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J312" s="5" t="n">
         <v>0.021705</v>
       </c>
-      <c r="K305" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L305" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M305" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N305" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O305" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P305" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q305" t="inlineStr">
+      <c r="K312" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L312" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M312" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N312" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O312" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P312" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q312" t="inlineStr">
         <is>
           <t>-</t>
         </is>
